--- a/Dados/table_PROD_BR_ANUAL_1_aux.xlsx
+++ b/Dados/table_PROD_BR_ANUAL_1_aux.xlsx
@@ -11,12 +11,18 @@
     <sheet name="n" sheetId="2" r:id="rId2"/>
     <sheet name="hb" sheetId="3" r:id="rId3"/>
     <sheet name="ef" sheetId="4" r:id="rId4"/>
-    <sheet name="n_p_cv" sheetId="5" r:id="rId5"/>
-    <sheet name="hb_p_cv" sheetId="6" r:id="rId6"/>
-    <sheet name="ef_p_cv" sheetId="7" r:id="rId7"/>
-    <sheet name="n_s_cv" sheetId="8" r:id="rId8"/>
-    <sheet name="hb_s_cv" sheetId="9" r:id="rId9"/>
-    <sheet name="ef_s_cv" sheetId="10" r:id="rId10"/>
+    <sheet name="n_p" sheetId="5" r:id="rId5"/>
+    <sheet name="hb_p" sheetId="6" r:id="rId6"/>
+    <sheet name="ef_p" sheetId="7" r:id="rId7"/>
+    <sheet name="n_s" sheetId="8" r:id="rId8"/>
+    <sheet name="hb_s" sheetId="9" r:id="rId9"/>
+    <sheet name="ef_s" sheetId="10" r:id="rId10"/>
+    <sheet name="n_p_cv" sheetId="11" r:id="rId11"/>
+    <sheet name="hb_p_cv" sheetId="12" r:id="rId12"/>
+    <sheet name="ef_p_cv" sheetId="13" r:id="rId13"/>
+    <sheet name="n_s_cv" sheetId="14" r:id="rId14"/>
+    <sheet name="hb_s_cv" sheetId="15" r:id="rId15"/>
+    <sheet name="ef_s_cv" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1223,6 +1229,4029 @@
         </is>
       </c>
       <c r="B2">
+        <v>583814.81168922</v>
+      </c>
+      <c r="C2">
+        <v>10721.39398632</v>
+      </c>
+      <c r="D2">
+        <v>216417.58135496</v>
+      </c>
+      <c r="E2">
+        <v>15978.66760238</v>
+      </c>
+      <c r="F2">
+        <v>138984.10384426</v>
+      </c>
+      <c r="G2">
+        <v>299072.96838004</v>
+      </c>
+      <c r="H2">
+        <v>112800.00907481</v>
+      </c>
+      <c r="I2">
+        <v>60164.93199269</v>
+      </c>
+      <c r="J2">
+        <v>8678.53267692</v>
+      </c>
+      <c r="K2">
+        <v>25578.8187439</v>
+      </c>
+      <c r="L2">
+        <v>1293831.47751996</v>
+      </c>
+      <c r="M2">
+        <v>787519.43209632</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>643494.82347909</v>
+      </c>
+      <c r="C3">
+        <v>6379.15036752</v>
+      </c>
+      <c r="D3">
+        <v>201229.66771184</v>
+      </c>
+      <c r="F3">
+        <v>153640.47470018</v>
+      </c>
+      <c r="G3">
+        <v>288280.0130007</v>
+      </c>
+      <c r="H3">
+        <v>127051.00913345</v>
+      </c>
+      <c r="I3">
+        <v>58894.71622678</v>
+      </c>
+      <c r="J3">
+        <v>21249.1742966</v>
+      </c>
+      <c r="K3">
+        <v>47587.546159</v>
+      </c>
+      <c r="L3">
+        <v>1569307.02241102</v>
+      </c>
+      <c r="M3">
+        <v>826940.00866107</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>607851.90474387</v>
+      </c>
+      <c r="C4">
+        <v>2780.50693607</v>
+      </c>
+      <c r="D4">
+        <v>208288.18331371</v>
+      </c>
+      <c r="F4">
+        <v>216850.79772527</v>
+      </c>
+      <c r="G4">
+        <v>402309.80853225</v>
+      </c>
+      <c r="H4">
+        <v>129738.43667691</v>
+      </c>
+      <c r="I4">
+        <v>45228.83770787</v>
+      </c>
+      <c r="J4">
+        <v>6790.762949739999</v>
+      </c>
+      <c r="K4">
+        <v>55523.1044049</v>
+      </c>
+      <c r="L4">
+        <v>1537082.77645996</v>
+      </c>
+      <c r="M4">
+        <v>754598.96632687</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>680525.1910028399</v>
+      </c>
+      <c r="D5">
+        <v>201709.14360692</v>
+      </c>
+      <c r="F5">
+        <v>101349.53122512</v>
+      </c>
+      <c r="G5">
+        <v>468526.3967978</v>
+      </c>
+      <c r="H5">
+        <v>119606.15781099</v>
+      </c>
+      <c r="I5">
+        <v>13833.60064455</v>
+      </c>
+      <c r="J5">
+        <v>13161.09105555</v>
+      </c>
+      <c r="K5">
+        <v>3641.4020217</v>
+      </c>
+      <c r="L5">
+        <v>1438198.0414195</v>
+      </c>
+      <c r="M5">
+        <v>862453.5656565099</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>685716.5898272</v>
+      </c>
+      <c r="D6">
+        <v>183749.28406113</v>
+      </c>
+      <c r="E6">
+        <v>6359.79873984</v>
+      </c>
+      <c r="F6">
+        <v>43329.64727679</v>
+      </c>
+      <c r="G6">
+        <v>292240.5410903</v>
+      </c>
+      <c r="H6">
+        <v>170327.48062912</v>
+      </c>
+      <c r="I6">
+        <v>20441.4733226</v>
+      </c>
+      <c r="J6">
+        <v>3378.70620944</v>
+      </c>
+      <c r="K6">
+        <v>8996.764264450001</v>
+      </c>
+      <c r="L6">
+        <v>1205030.43579473</v>
+      </c>
+      <c r="M6">
+        <v>760114.3135363901</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1006701.75150813</v>
+      </c>
+      <c r="D7">
+        <v>106941.06526063</v>
+      </c>
+      <c r="F7">
+        <v>119641.02562997</v>
+      </c>
+      <c r="G7">
+        <v>310901.41894156</v>
+      </c>
+      <c r="H7">
+        <v>206923.27417051</v>
+      </c>
+      <c r="I7">
+        <v>35020.50383218</v>
+      </c>
+      <c r="J7">
+        <v>3425.3936989</v>
+      </c>
+      <c r="K7">
+        <v>38096.68472073</v>
+      </c>
+      <c r="L7">
+        <v>1495157.22970122</v>
+      </c>
+      <c r="M7">
+        <v>703485.09210506</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>922225.23289676</v>
+      </c>
+      <c r="D8">
+        <v>229146.10883338</v>
+      </c>
+      <c r="E8">
+        <v>6979.60466304</v>
+      </c>
+      <c r="F8">
+        <v>167684.48656045</v>
+      </c>
+      <c r="G8">
+        <v>495178.28649823</v>
+      </c>
+      <c r="H8">
+        <v>168251.84747807</v>
+      </c>
+      <c r="I8">
+        <v>30452.24189459</v>
+      </c>
+      <c r="J8">
+        <v>4066.7076715</v>
+      </c>
+      <c r="K8">
+        <v>18383.9978713</v>
+      </c>
+      <c r="L8">
+        <v>1405201.93606059</v>
+      </c>
+      <c r="M8">
+        <v>619014.1840727601</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>876964.77008589</v>
+      </c>
+      <c r="C9">
+        <v>1709.0309305</v>
+      </c>
+      <c r="D9">
+        <v>169780.48876886</v>
+      </c>
+      <c r="F9">
+        <v>94508.41933749001</v>
+      </c>
+      <c r="G9">
+        <v>409351.67970699</v>
+      </c>
+      <c r="H9">
+        <v>125886.74184034</v>
+      </c>
+      <c r="I9">
+        <v>40033.3017117</v>
+      </c>
+      <c r="J9">
+        <v>31296.12663786</v>
+      </c>
+      <c r="K9">
+        <v>25166.0217987</v>
+      </c>
+      <c r="L9">
+        <v>1562965.88992476</v>
+      </c>
+      <c r="M9">
+        <v>605475.6215637</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>760117.36201863</v>
+      </c>
+      <c r="D10">
+        <v>63854.48843452</v>
+      </c>
+      <c r="F10">
+        <v>49699.47982741</v>
+      </c>
+      <c r="G10">
+        <v>199040.33616225</v>
+      </c>
+      <c r="H10">
+        <v>29402.48970306</v>
+      </c>
+      <c r="I10">
+        <v>61572.62392021</v>
+      </c>
+      <c r="J10">
+        <v>5971.0621158</v>
+      </c>
+      <c r="K10">
+        <v>15014.322301</v>
+      </c>
+      <c r="L10">
+        <v>1018673.07453573</v>
+      </c>
+      <c r="M10">
+        <v>560986.2057704501</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>413119.50338783</v>
+      </c>
+      <c r="C11">
+        <v>9153.413098200001</v>
+      </c>
+      <c r="D11">
+        <v>96862.16337567</v>
+      </c>
+      <c r="F11">
+        <v>79974.19949494</v>
+      </c>
+      <c r="G11">
+        <v>472837.92475486</v>
+      </c>
+      <c r="H11">
+        <v>60623.62806593</v>
+      </c>
+      <c r="I11">
+        <v>72477.73591592</v>
+      </c>
+      <c r="J11">
+        <v>6711.7199208</v>
+      </c>
+      <c r="K11">
+        <v>8413.024689280001</v>
+      </c>
+      <c r="L11">
+        <v>933615.11314736</v>
+      </c>
+      <c r="M11">
+        <v>576019.5614699</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>600137.4902832099</v>
+      </c>
+      <c r="C12">
+        <v>4717.95226911</v>
+      </c>
+      <c r="D12">
+        <v>135710.79162629</v>
+      </c>
+      <c r="F12">
+        <v>61891.03584894</v>
+      </c>
+      <c r="G12">
+        <v>371432.54265078</v>
+      </c>
+      <c r="H12">
+        <v>112199.56714415</v>
+      </c>
+      <c r="I12">
+        <v>95130.37878756999</v>
+      </c>
+      <c r="J12">
+        <v>21227.34482008</v>
+      </c>
+      <c r="K12">
+        <v>50575.2773875</v>
+      </c>
+      <c r="L12">
+        <v>1164824.36090757</v>
+      </c>
+      <c r="M12">
+        <v>643933.65687156</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>584149.0743460701</v>
+      </c>
+      <c r="D13">
+        <v>167017.26489313</v>
+      </c>
+      <c r="E13">
+        <v>13116.4635492</v>
+      </c>
+      <c r="F13">
+        <v>90942.35883608001</v>
+      </c>
+      <c r="G13">
+        <v>336324.27213147</v>
+      </c>
+      <c r="H13">
+        <v>208331.46685906</v>
+      </c>
+      <c r="I13">
+        <v>106205.58981997</v>
+      </c>
+      <c r="J13">
+        <v>67908.35641492999</v>
+      </c>
+      <c r="K13">
+        <v>5157.5317434</v>
+      </c>
+      <c r="L13">
+        <v>1720442.723001</v>
+      </c>
+      <c r="M13">
+        <v>583573.66931905</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>580871.43786482</v>
+      </c>
+      <c r="D14">
+        <v>227480.23274883</v>
+      </c>
+      <c r="E14">
+        <v>11263.33294488</v>
+      </c>
+      <c r="F14">
+        <v>109199.70932221</v>
+      </c>
+      <c r="G14">
+        <v>545562.1525235299</v>
+      </c>
+      <c r="H14">
+        <v>233204.15654568</v>
+      </c>
+      <c r="I14">
+        <v>138080.62127203</v>
+      </c>
+      <c r="J14">
+        <v>75246.25260681</v>
+      </c>
+      <c r="K14">
+        <v>38053.28388012</v>
+      </c>
+      <c r="L14">
+        <v>1818599.23634789</v>
+      </c>
+      <c r="M14">
+        <v>631100.4219671</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>1650772.71585219</v>
+      </c>
+      <c r="D15">
+        <v>455009.12749454</v>
+      </c>
+      <c r="F15">
+        <v>320470.3431503</v>
+      </c>
+      <c r="G15">
+        <v>1139583.46453642</v>
+      </c>
+      <c r="H15">
+        <v>553482.05657221</v>
+      </c>
+      <c r="I15">
+        <v>261651.78679219</v>
+      </c>
+      <c r="J15">
+        <v>36522.58701203</v>
+      </c>
+      <c r="K15">
+        <v>153615.1244399</v>
+      </c>
+      <c r="L15">
+        <v>5444851.9039135</v>
+      </c>
+      <c r="M15">
+        <v>2175313.80843183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1.229509306061297</v>
+      </c>
+      <c r="C2">
+        <v>5.422895149107467</v>
+      </c>
+      <c r="D2">
+        <v>1.132517873130095</v>
+      </c>
+      <c r="E2">
+        <v>3.48050920527917</v>
+      </c>
+      <c r="F2">
+        <v>1.16087179542573</v>
+      </c>
+      <c r="G2">
+        <v>0.8026298210845056</v>
+      </c>
+      <c r="H2">
+        <v>1.530397174176123</v>
+      </c>
+      <c r="I2">
+        <v>3.634789800402286</v>
+      </c>
+      <c r="J2">
+        <v>3.485185464514529</v>
+      </c>
+      <c r="K2">
+        <v>4.559033770657147</v>
+      </c>
+      <c r="L2">
+        <v>0.5720107879756813</v>
+      </c>
+      <c r="M2">
+        <v>1.075411208719432</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1.145909126694403</v>
+      </c>
+      <c r="C3">
+        <v>5.600027380663285</v>
+      </c>
+      <c r="D3">
+        <v>1.1544791780968</v>
+      </c>
+      <c r="E3">
+        <v>3.313489361712263</v>
+      </c>
+      <c r="F3">
+        <v>1.107356488965733</v>
+      </c>
+      <c r="G3">
+        <v>0.7556625881647681</v>
+      </c>
+      <c r="H3">
+        <v>1.662705434518929</v>
+      </c>
+      <c r="I3">
+        <v>3.343277578646285</v>
+      </c>
+      <c r="J3">
+        <v>3.067822707257595</v>
+      </c>
+      <c r="K3">
+        <v>4.268825398506164</v>
+      </c>
+      <c r="L3">
+        <v>0.5576023476828285</v>
+      </c>
+      <c r="M3">
+        <v>1.114799324266599</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1.289928248091808</v>
+      </c>
+      <c r="C4">
+        <v>4.684193230397252</v>
+      </c>
+      <c r="D4">
+        <v>1.271465392402865</v>
+      </c>
+      <c r="E4">
+        <v>3.422182276402452</v>
+      </c>
+      <c r="F4">
+        <v>1.349662438642522</v>
+      </c>
+      <c r="G4">
+        <v>0.8145465260978322</v>
+      </c>
+      <c r="H4">
+        <v>1.704634590636747</v>
+      </c>
+      <c r="I4">
+        <v>3.26803690089042</v>
+      </c>
+      <c r="J4">
+        <v>3.581326736320688</v>
+      </c>
+      <c r="K4">
+        <v>5.309476692836358</v>
+      </c>
+      <c r="L4">
+        <v>0.627884114225734</v>
+      </c>
+      <c r="M4">
+        <v>1.117192123712726</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1.245579554740835</v>
+      </c>
+      <c r="C5">
+        <v>5.916611759372524</v>
+      </c>
+      <c r="D5">
+        <v>1.235992549751658</v>
+      </c>
+      <c r="E5">
+        <v>3.41474354148054</v>
+      </c>
+      <c r="F5">
+        <v>1.407216410652225</v>
+      </c>
+      <c r="G5">
+        <v>0.8013147417887808</v>
+      </c>
+      <c r="H5">
+        <v>1.631364805663721</v>
+      </c>
+      <c r="I5">
+        <v>3.060597517936308</v>
+      </c>
+      <c r="J5">
+        <v>3.182892098083798</v>
+      </c>
+      <c r="K5">
+        <v>5.013767820466216</v>
+      </c>
+      <c r="L5">
+        <v>0.6176146613340081</v>
+      </c>
+      <c r="M5">
+        <v>1.018165437043274</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1.36690774103845</v>
+      </c>
+      <c r="C6">
+        <v>6.06591524225312</v>
+      </c>
+      <c r="D6">
+        <v>1.417790824902772</v>
+      </c>
+      <c r="E6">
+        <v>5.096847185389179</v>
+      </c>
+      <c r="F6">
+        <v>1.383345398251238</v>
+      </c>
+      <c r="G6">
+        <v>0.8336520026707435</v>
+      </c>
+      <c r="H6">
+        <v>1.843682935078834</v>
+      </c>
+      <c r="I6">
+        <v>3.485078902382059</v>
+      </c>
+      <c r="J6">
+        <v>5.082178678255985</v>
+      </c>
+      <c r="K6">
+        <v>4.625380152230658</v>
+      </c>
+      <c r="L6">
+        <v>0.7287056942710369</v>
+      </c>
+      <c r="M6">
+        <v>1.180518958176392</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1.57842999874379</v>
+      </c>
+      <c r="C7">
+        <v>5.557745595622676</v>
+      </c>
+      <c r="D7">
+        <v>1.26933219910818</v>
+      </c>
+      <c r="E7">
+        <v>4.045237745523112</v>
+      </c>
+      <c r="F7">
+        <v>1.381736865000149</v>
+      </c>
+      <c r="G7">
+        <v>0.8667098488719912</v>
+      </c>
+      <c r="H7">
+        <v>1.612149727079564</v>
+      </c>
+      <c r="I7">
+        <v>3.598827662304359</v>
+      </c>
+      <c r="J7">
+        <v>3.903767301729239</v>
+      </c>
+      <c r="K7">
+        <v>4.347414711761307</v>
+      </c>
+      <c r="L7">
+        <v>0.6656510678540066</v>
+      </c>
+      <c r="M7">
+        <v>1.048312678150514</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1.303883805551855</v>
+      </c>
+      <c r="C8">
+        <v>6.067357533031254</v>
+      </c>
+      <c r="D8">
+        <v>1.403372048619912</v>
+      </c>
+      <c r="E8">
+        <v>4.057611668795655</v>
+      </c>
+      <c r="F8">
+        <v>1.213744574905402</v>
+      </c>
+      <c r="G8">
+        <v>0.8442317228751375</v>
+      </c>
+      <c r="H8">
+        <v>1.620853768828055</v>
+      </c>
+      <c r="I8">
+        <v>3.332152888587812</v>
+      </c>
+      <c r="J8">
+        <v>3.614013788234624</v>
+      </c>
+      <c r="K8">
+        <v>4.964861376404981</v>
+      </c>
+      <c r="L8">
+        <v>0.6217800534006352</v>
+      </c>
+      <c r="M8">
+        <v>1.061189345053169</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>1.51241940713255</v>
+      </c>
+      <c r="C9">
+        <v>4.924461460619824</v>
+      </c>
+      <c r="D9">
+        <v>1.179607521473681</v>
+      </c>
+      <c r="E9">
+        <v>4.082277459013457</v>
+      </c>
+      <c r="F9">
+        <v>1.284583405392732</v>
+      </c>
+      <c r="G9">
+        <v>0.857982131618952</v>
+      </c>
+      <c r="H9">
+        <v>1.5277165853577</v>
+      </c>
+      <c r="I9">
+        <v>3.290042847848384</v>
+      </c>
+      <c r="J9">
+        <v>3.277534660268102</v>
+      </c>
+      <c r="K9">
+        <v>4.47913374434104</v>
+      </c>
+      <c r="L9">
+        <v>0.623405736057393</v>
+      </c>
+      <c r="M9">
+        <v>1.113967901304608</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>1.770448501411388</v>
+      </c>
+      <c r="C10">
+        <v>7.922132798221261</v>
+      </c>
+      <c r="D10">
+        <v>1.432295248209979</v>
+      </c>
+      <c r="E10">
+        <v>4.511625670624748</v>
+      </c>
+      <c r="F10">
+        <v>1.494292874704401</v>
+      </c>
+      <c r="G10">
+        <v>0.9218973301385383</v>
+      </c>
+      <c r="H10">
+        <v>1.970170568040978</v>
+      </c>
+      <c r="I10">
+        <v>3.851741525271372</v>
+      </c>
+      <c r="J10">
+        <v>3.571980518068966</v>
+      </c>
+      <c r="K10">
+        <v>5.819594722840173</v>
+      </c>
+      <c r="L10">
+        <v>0.7850082761908487</v>
+      </c>
+      <c r="M10">
+        <v>1.256948504275537</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>1.756787229900745</v>
+      </c>
+      <c r="C11">
+        <v>6.842685300827355</v>
+      </c>
+      <c r="D11">
+        <v>1.659444269398046</v>
+      </c>
+      <c r="E11">
+        <v>4.820188068413774</v>
+      </c>
+      <c r="F11">
+        <v>1.691186809373708</v>
+      </c>
+      <c r="G11">
+        <v>1.01260330005212</v>
+      </c>
+      <c r="H11">
+        <v>2.086724149174064</v>
+      </c>
+      <c r="I11">
+        <v>3.59522377877838</v>
+      </c>
+      <c r="J11">
+        <v>4.60873951191647</v>
+      </c>
+      <c r="K11">
+        <v>6.265700312288332</v>
+      </c>
+      <c r="L11">
+        <v>0.8007165448416614</v>
+      </c>
+      <c r="M11">
+        <v>1.359065990292055</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>1.972930386400396</v>
+      </c>
+      <c r="C12">
+        <v>5.908265861290106</v>
+      </c>
+      <c r="D12">
+        <v>1.346142466789208</v>
+      </c>
+      <c r="E12">
+        <v>4.473131116686156</v>
+      </c>
+      <c r="F12">
+        <v>1.470576736620326</v>
+      </c>
+      <c r="G12">
+        <v>0.899481591222253</v>
+      </c>
+      <c r="H12">
+        <v>1.706510729568999</v>
+      </c>
+      <c r="I12">
+        <v>3.340128457392646</v>
+      </c>
+      <c r="J12">
+        <v>3.826703262115062</v>
+      </c>
+      <c r="K12">
+        <v>5.247752198612668</v>
+      </c>
+      <c r="L12">
+        <v>0.6707843710798715</v>
+      </c>
+      <c r="M12">
+        <v>1.078536333383202</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>1.656838535675915</v>
+      </c>
+      <c r="C13">
+        <v>7.054917103522541</v>
+      </c>
+      <c r="D13">
+        <v>1.434872988288003</v>
+      </c>
+      <c r="E13">
+        <v>4.861737091937679</v>
+      </c>
+      <c r="F13">
+        <v>1.490415948086583</v>
+      </c>
+      <c r="G13">
+        <v>0.8900361303720983</v>
+      </c>
+      <c r="H13">
+        <v>1.71408683243416</v>
+      </c>
+      <c r="I13">
+        <v>3.196475143018311</v>
+      </c>
+      <c r="J13">
+        <v>3.528636029218449</v>
+      </c>
+      <c r="K13">
+        <v>4.71258680424362</v>
+      </c>
+      <c r="L13">
+        <v>0.5963896972469169</v>
+      </c>
+      <c r="M13">
+        <v>1.19136228413636</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>1.573054290823048</v>
+      </c>
+      <c r="C14">
+        <v>5.775015592394986</v>
+      </c>
+      <c r="D14">
+        <v>1.448052037880141</v>
+      </c>
+      <c r="E14">
+        <v>3.893389754353624</v>
+      </c>
+      <c r="F14">
+        <v>1.136727461094893</v>
+      </c>
+      <c r="G14">
+        <v>0.8512893678858247</v>
+      </c>
+      <c r="H14">
+        <v>1.490994169233142</v>
+      </c>
+      <c r="I14">
+        <v>2.812658987198598</v>
+      </c>
+      <c r="J14">
+        <v>3.559050133612009</v>
+      </c>
+      <c r="K14">
+        <v>4.937871702839121</v>
+      </c>
+      <c r="L14">
+        <v>0.6100656000659873</v>
+      </c>
+      <c r="M14">
+        <v>1.083759406392644</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>0.8219250263801855</v>
+      </c>
+      <c r="C15">
+        <v>2.828888800341245</v>
+      </c>
+      <c r="D15">
+        <v>0.6124977714940172</v>
+      </c>
+      <c r="E15">
+        <v>2.161028073972597</v>
+      </c>
+      <c r="F15">
+        <v>0.7518038954981799</v>
+      </c>
+      <c r="G15">
+        <v>0.4221341049249467</v>
+      </c>
+      <c r="H15">
+        <v>0.8895251141264583</v>
+      </c>
+      <c r="I15">
+        <v>1.429619085615528</v>
+      </c>
+      <c r="J15">
+        <v>1.664082672826958</v>
+      </c>
+      <c r="K15">
+        <v>2.478289220100647</v>
+      </c>
+      <c r="L15">
+        <v>0.3423464876062325</v>
+      </c>
+      <c r="M15">
+        <v>0.5490223231706377</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1.314362904276624</v>
+      </c>
+      <c r="C2">
+        <v>5.624013373672638</v>
+      </c>
+      <c r="D2">
+        <v>1.185261311493225</v>
+      </c>
+      <c r="E2">
+        <v>3.640733733499985</v>
+      </c>
+      <c r="F2">
+        <v>1.194570504447914</v>
+      </c>
+      <c r="G2">
+        <v>0.8565255809558048</v>
+      </c>
+      <c r="H2">
+        <v>1.662252503360129</v>
+      </c>
+      <c r="I2">
+        <v>3.674858805236258</v>
+      </c>
+      <c r="J2">
+        <v>3.613502185656624</v>
+      </c>
+      <c r="K2">
+        <v>4.837207260812677</v>
+      </c>
+      <c r="L2">
+        <v>0.656422943442294</v>
+      </c>
+      <c r="M2">
+        <v>1.110160418304029</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1.209365973696709</v>
+      </c>
+      <c r="C3">
+        <v>5.864605027722864</v>
+      </c>
+      <c r="D3">
+        <v>1.199130166701676</v>
+      </c>
+      <c r="E3">
+        <v>3.428093625864266</v>
+      </c>
+      <c r="F3">
+        <v>1.144230160552132</v>
+      </c>
+      <c r="G3">
+        <v>0.7889672856494976</v>
+      </c>
+      <c r="H3">
+        <v>1.712039266091775</v>
+      </c>
+      <c r="I3">
+        <v>3.625167657681468</v>
+      </c>
+      <c r="J3">
+        <v>3.135811199746726</v>
+      </c>
+      <c r="K3">
+        <v>4.633584072734922</v>
+      </c>
+      <c r="L3">
+        <v>0.6357284122973624</v>
+      </c>
+      <c r="M3">
+        <v>1.153462473577575</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1.358847473116001</v>
+      </c>
+      <c r="C4">
+        <v>4.608659910007755</v>
+      </c>
+      <c r="D4">
+        <v>1.28594618532278</v>
+      </c>
+      <c r="E4">
+        <v>3.559617464309491</v>
+      </c>
+      <c r="F4">
+        <v>1.356986461902464</v>
+      </c>
+      <c r="G4">
+        <v>0.8254632641116486</v>
+      </c>
+      <c r="H4">
+        <v>1.728551864759313</v>
+      </c>
+      <c r="I4">
+        <v>3.455468827521229</v>
+      </c>
+      <c r="J4">
+        <v>3.610989419289638</v>
+      </c>
+      <c r="K4">
+        <v>5.828042273809888</v>
+      </c>
+      <c r="L4">
+        <v>0.6918545988700235</v>
+      </c>
+      <c r="M4">
+        <v>1.168985166637366</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1.295786108582208</v>
+      </c>
+      <c r="C5">
+        <v>5.781807814151331</v>
+      </c>
+      <c r="D5">
+        <v>1.304699055190227</v>
+      </c>
+      <c r="E5">
+        <v>3.676838558459818</v>
+      </c>
+      <c r="F5">
+        <v>1.452628989414401</v>
+      </c>
+      <c r="G5">
+        <v>0.8443945556070273</v>
+      </c>
+      <c r="H5">
+        <v>1.710679608013757</v>
+      </c>
+      <c r="I5">
+        <v>3.186937776499812</v>
+      </c>
+      <c r="J5">
+        <v>3.322618485857675</v>
+      </c>
+      <c r="K5">
+        <v>5.060266596289079</v>
+      </c>
+      <c r="L5">
+        <v>0.6985459937766789</v>
+      </c>
+      <c r="M5">
+        <v>1.082412442624864</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1.452558082071599</v>
+      </c>
+      <c r="C6">
+        <v>5.997073175351049</v>
+      </c>
+      <c r="D6">
+        <v>1.440568486417168</v>
+      </c>
+      <c r="E6">
+        <v>5.305866218884682</v>
+      </c>
+      <c r="F6">
+        <v>1.437828280894304</v>
+      </c>
+      <c r="G6">
+        <v>0.8856491432736457</v>
+      </c>
+      <c r="H6">
+        <v>1.83648067475091</v>
+      </c>
+      <c r="I6">
+        <v>3.532400159055796</v>
+      </c>
+      <c r="J6">
+        <v>5.251337622969313</v>
+      </c>
+      <c r="K6">
+        <v>4.853203324395947</v>
+      </c>
+      <c r="L6">
+        <v>0.7663323393924406</v>
+      </c>
+      <c r="M6">
+        <v>1.200736138632501</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1.723286455445459</v>
+      </c>
+      <c r="C7">
+        <v>5.537053082648635</v>
+      </c>
+      <c r="D7">
+        <v>1.322496640906426</v>
+      </c>
+      <c r="E7">
+        <v>3.862628375052267</v>
+      </c>
+      <c r="F7">
+        <v>1.404933544316567</v>
+      </c>
+      <c r="G7">
+        <v>0.8914392741006216</v>
+      </c>
+      <c r="H7">
+        <v>1.668134473785199</v>
+      </c>
+      <c r="I7">
+        <v>3.740862104781189</v>
+      </c>
+      <c r="J7">
+        <v>3.959094880669738</v>
+      </c>
+      <c r="K7">
+        <v>4.482010031351503</v>
+      </c>
+      <c r="L7">
+        <v>0.7309274083309352</v>
+      </c>
+      <c r="M7">
+        <v>1.090482662017584</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1.401826221762044</v>
+      </c>
+      <c r="C8">
+        <v>6.10029947942409</v>
+      </c>
+      <c r="D8">
+        <v>1.44429101603097</v>
+      </c>
+      <c r="E8">
+        <v>4.023931040476961</v>
+      </c>
+      <c r="F8">
+        <v>1.263133575304094</v>
+      </c>
+      <c r="G8">
+        <v>0.9135861177445659</v>
+      </c>
+      <c r="H8">
+        <v>1.753375622555582</v>
+      </c>
+      <c r="I8">
+        <v>3.471056088971512</v>
+      </c>
+      <c r="J8">
+        <v>3.754212598177478</v>
+      </c>
+      <c r="K8">
+        <v>5.305156793080918</v>
+      </c>
+      <c r="L8">
+        <v>0.7225256073406711</v>
+      </c>
+      <c r="M8">
+        <v>1.085149469580358</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>1.638682473558011</v>
+      </c>
+      <c r="C9">
+        <v>5.063181003422212</v>
+      </c>
+      <c r="D9">
+        <v>1.226381160701225</v>
+      </c>
+      <c r="E9">
+        <v>4.015043996618119</v>
+      </c>
+      <c r="F9">
+        <v>1.361185206787635</v>
+      </c>
+      <c r="G9">
+        <v>0.8862266980726554</v>
+      </c>
+      <c r="H9">
+        <v>1.633889242678157</v>
+      </c>
+      <c r="I9">
+        <v>3.406168943776743</v>
+      </c>
+      <c r="J9">
+        <v>3.443799826253133</v>
+      </c>
+      <c r="K9">
+        <v>4.685332002871649</v>
+      </c>
+      <c r="L9">
+        <v>0.6916745269833164</v>
+      </c>
+      <c r="M9">
+        <v>1.132221240548153</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>1.924560714078346</v>
+      </c>
+      <c r="C10">
+        <v>7.986339015503703</v>
+      </c>
+      <c r="D10">
+        <v>1.502441303672767</v>
+      </c>
+      <c r="E10">
+        <v>4.548931694587989</v>
+      </c>
+      <c r="F10">
+        <v>1.527918343828601</v>
+      </c>
+      <c r="G10">
+        <v>0.920583112562974</v>
+      </c>
+      <c r="H10">
+        <v>2.011702199770191</v>
+      </c>
+      <c r="I10">
+        <v>3.98888836219614</v>
+      </c>
+      <c r="J10">
+        <v>3.684415938264253</v>
+      </c>
+      <c r="K10">
+        <v>5.888869771801783</v>
+      </c>
+      <c r="L10">
+        <v>0.8671276060074106</v>
+      </c>
+      <c r="M10">
+        <v>1.27562436525766</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>1.948623552848866</v>
+      </c>
+      <c r="C11">
+        <v>6.970428238489861</v>
+      </c>
+      <c r="D11">
+        <v>1.672239201632864</v>
+      </c>
+      <c r="E11">
+        <v>4.944690233067396</v>
+      </c>
+      <c r="F11">
+        <v>1.7422154373825</v>
+      </c>
+      <c r="G11">
+        <v>1.081207125435421</v>
+      </c>
+      <c r="H11">
+        <v>2.203990314057491</v>
+      </c>
+      <c r="I11">
+        <v>3.66346617520867</v>
+      </c>
+      <c r="J11">
+        <v>4.899626414403922</v>
+      </c>
+      <c r="K11">
+        <v>6.483398151383837</v>
+      </c>
+      <c r="L11">
+        <v>0.8918631105909106</v>
+      </c>
+      <c r="M11">
+        <v>1.373195938709162</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>1.92619603271823</v>
+      </c>
+      <c r="C12">
+        <v>6.025587035886979</v>
+      </c>
+      <c r="D12">
+        <v>1.415326353718094</v>
+      </c>
+      <c r="E12">
+        <v>4.458790941810822</v>
+      </c>
+      <c r="F12">
+        <v>1.50300894969205</v>
+      </c>
+      <c r="G12">
+        <v>0.9285480188636875</v>
+      </c>
+      <c r="H12">
+        <v>1.852531593458228</v>
+      </c>
+      <c r="I12">
+        <v>3.477010562101077</v>
+      </c>
+      <c r="J12">
+        <v>3.985825969827106</v>
+      </c>
+      <c r="K12">
+        <v>5.485150124811742</v>
+      </c>
+      <c r="L12">
+        <v>0.7329861141513896</v>
+      </c>
+      <c r="M12">
+        <v>1.138217257955315</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>1.819936790958393</v>
+      </c>
+      <c r="C13">
+        <v>6.991798980622777</v>
+      </c>
+      <c r="D13">
+        <v>1.495690834930072</v>
+      </c>
+      <c r="E13">
+        <v>4.891730512840009</v>
+      </c>
+      <c r="F13">
+        <v>1.560637326786331</v>
+      </c>
+      <c r="G13">
+        <v>0.9414849592320836</v>
+      </c>
+      <c r="H13">
+        <v>1.761887882809969</v>
+      </c>
+      <c r="I13">
+        <v>3.253118401568827</v>
+      </c>
+      <c r="J13">
+        <v>3.626275208150731</v>
+      </c>
+      <c r="K13">
+        <v>4.837148174263797</v>
+      </c>
+      <c r="L13">
+        <v>0.6972026071527506</v>
+      </c>
+      <c r="M13">
+        <v>1.250741035052319</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>1.671353322476085</v>
+      </c>
+      <c r="C14">
+        <v>5.682299260829111</v>
+      </c>
+      <c r="D14">
+        <v>1.520874858780017</v>
+      </c>
+      <c r="E14">
+        <v>3.945699332256952</v>
+      </c>
+      <c r="F14">
+        <v>1.179360264513972</v>
+      </c>
+      <c r="G14">
+        <v>0.9247358516158158</v>
+      </c>
+      <c r="H14">
+        <v>1.558962472815284</v>
+      </c>
+      <c r="I14">
+        <v>2.865592505559784</v>
+      </c>
+      <c r="J14">
+        <v>3.707098843407498</v>
+      </c>
+      <c r="K14">
+        <v>5.200210501392466</v>
+      </c>
+      <c r="L14">
+        <v>0.6766218143124243</v>
+      </c>
+      <c r="M14">
+        <v>1.093303390373478</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>0.8999678015670664</v>
+      </c>
+      <c r="C15">
+        <v>2.813963177507366</v>
+      </c>
+      <c r="D15">
+        <v>0.6395298716481574</v>
+      </c>
+      <c r="E15">
+        <v>2.228962182796911</v>
+      </c>
+      <c r="F15">
+        <v>0.799710715001933</v>
+      </c>
+      <c r="G15">
+        <v>0.4592090784211751</v>
+      </c>
+      <c r="H15">
+        <v>0.9249966893057747</v>
+      </c>
+      <c r="I15">
+        <v>1.43913912459358</v>
+      </c>
+      <c r="J15">
+        <v>1.723133202358719</v>
+      </c>
+      <c r="K15">
+        <v>2.609372426026087</v>
+      </c>
+      <c r="L15">
+        <v>0.3810541173167093</v>
+      </c>
+      <c r="M15">
+        <v>0.5570082515932762</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1.305006849996661</v>
+      </c>
+      <c r="C2">
+        <v>5.653509282231969</v>
+      </c>
+      <c r="D2">
+        <v>1.197306302273826</v>
+      </c>
+      <c r="E2">
+        <v>3.668857617627128</v>
+      </c>
+      <c r="F2">
+        <v>1.195180785135504</v>
+      </c>
+      <c r="G2">
+        <v>0.8779734722253659</v>
+      </c>
+      <c r="H2">
+        <v>1.680349563209922</v>
+      </c>
+      <c r="I2">
+        <v>3.77462609993864</v>
+      </c>
+      <c r="J2">
+        <v>3.667363136725615</v>
+      </c>
+      <c r="K2">
+        <v>4.988691871370069</v>
+      </c>
+      <c r="L2">
+        <v>0.6709603721965898</v>
+      </c>
+      <c r="M2">
+        <v>1.1321813115778</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1.252336183638528</v>
+      </c>
+      <c r="C3">
+        <v>5.751911789310947</v>
+      </c>
+      <c r="D3">
+        <v>1.213421141156759</v>
+      </c>
+      <c r="E3">
+        <v>3.349157098690275</v>
+      </c>
+      <c r="F3">
+        <v>1.169532700932448</v>
+      </c>
+      <c r="G3">
+        <v>0.8038374123209355</v>
+      </c>
+      <c r="H3">
+        <v>1.776766519567841</v>
+      </c>
+      <c r="I3">
+        <v>3.669895651884866</v>
+      </c>
+      <c r="J3">
+        <v>3.166909075496505</v>
+      </c>
+      <c r="K3">
+        <v>4.740781709559833</v>
+      </c>
+      <c r="L3">
+        <v>0.6528519925100977</v>
+      </c>
+      <c r="M3">
+        <v>1.204533533498913</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1.359220133713039</v>
+      </c>
+      <c r="C4">
+        <v>4.701650814860233</v>
+      </c>
+      <c r="D4">
+        <v>1.299202243567142</v>
+      </c>
+      <c r="E4">
+        <v>3.553395210229854</v>
+      </c>
+      <c r="F4">
+        <v>1.391669211929121</v>
+      </c>
+      <c r="G4">
+        <v>0.8307040801180384</v>
+      </c>
+      <c r="H4">
+        <v>1.737588338881049</v>
+      </c>
+      <c r="I4">
+        <v>3.455649569770459</v>
+      </c>
+      <c r="J4">
+        <v>3.652792425811044</v>
+      </c>
+      <c r="K4">
+        <v>5.848595054747506</v>
+      </c>
+      <c r="L4">
+        <v>0.7100814491485826</v>
+      </c>
+      <c r="M4">
+        <v>1.184179007361313</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1.334018642497567</v>
+      </c>
+      <c r="C5">
+        <v>6.014963535817675</v>
+      </c>
+      <c r="D5">
+        <v>1.338943033058063</v>
+      </c>
+      <c r="E5">
+        <v>3.729428555311892</v>
+      </c>
+      <c r="F5">
+        <v>1.501638496183817</v>
+      </c>
+      <c r="G5">
+        <v>0.8672584823301503</v>
+      </c>
+      <c r="H5">
+        <v>1.750687528927887</v>
+      </c>
+      <c r="I5">
+        <v>3.271940604366938</v>
+      </c>
+      <c r="J5">
+        <v>3.309311273903474</v>
+      </c>
+      <c r="K5">
+        <v>5.12576589342913</v>
+      </c>
+      <c r="L5">
+        <v>0.7119088707655105</v>
+      </c>
+      <c r="M5">
+        <v>1.101132549397676</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1.489606244591462</v>
+      </c>
+      <c r="C6">
+        <v>5.849797506145743</v>
+      </c>
+      <c r="D6">
+        <v>1.459216757079727</v>
+      </c>
+      <c r="E6">
+        <v>5.464630470909245</v>
+      </c>
+      <c r="F6">
+        <v>1.456831829497377</v>
+      </c>
+      <c r="G6">
+        <v>0.8947745756012778</v>
+      </c>
+      <c r="H6">
+        <v>1.903347860279486</v>
+      </c>
+      <c r="I6">
+        <v>3.58737392613075</v>
+      </c>
+      <c r="J6">
+        <v>4.329577150910105</v>
+      </c>
+      <c r="K6">
+        <v>4.914921930090728</v>
+      </c>
+      <c r="L6">
+        <v>0.7931071223471037</v>
+      </c>
+      <c r="M6">
+        <v>1.210889539770282</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1.697520734876659</v>
+      </c>
+      <c r="C7">
+        <v>5.458507069989448</v>
+      </c>
+      <c r="D7">
+        <v>1.375129756485082</v>
+      </c>
+      <c r="E7">
+        <v>3.958865698264977</v>
+      </c>
+      <c r="F7">
+        <v>1.434339795381329</v>
+      </c>
+      <c r="G7">
+        <v>0.8759051760533968</v>
+      </c>
+      <c r="H7">
+        <v>1.677933055425201</v>
+      </c>
+      <c r="I7">
+        <v>3.862503674449367</v>
+      </c>
+      <c r="J7">
+        <v>3.89332510240765</v>
+      </c>
+      <c r="K7">
+        <v>4.63663707271178</v>
+      </c>
+      <c r="L7">
+        <v>0.7418336533483704</v>
+      </c>
+      <c r="M7">
+        <v>1.108480960519967</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1.416334095676617</v>
+      </c>
+      <c r="C8">
+        <v>6.194745140479269</v>
+      </c>
+      <c r="D8">
+        <v>1.474172993220126</v>
+      </c>
+      <c r="E8">
+        <v>4.135480850268473</v>
+      </c>
+      <c r="F8">
+        <v>1.26601978758067</v>
+      </c>
+      <c r="G8">
+        <v>0.9061201686906668</v>
+      </c>
+      <c r="H8">
+        <v>1.75251055601295</v>
+      </c>
+      <c r="I8">
+        <v>3.678170242991729</v>
+      </c>
+      <c r="J8">
+        <v>3.960382050391352</v>
+      </c>
+      <c r="K8">
+        <v>5.437967976303223</v>
+      </c>
+      <c r="L8">
+        <v>0.7375812932884701</v>
+      </c>
+      <c r="M8">
+        <v>1.125860881609441</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>1.650781155415802</v>
+      </c>
+      <c r="C9">
+        <v>5.222846107665599</v>
+      </c>
+      <c r="D9">
+        <v>1.243387540237515</v>
+      </c>
+      <c r="E9">
+        <v>4.067391890332972</v>
+      </c>
+      <c r="F9">
+        <v>1.394134984763305</v>
+      </c>
+      <c r="G9">
+        <v>0.9028503890142432</v>
+      </c>
+      <c r="H9">
+        <v>1.595319412359596</v>
+      </c>
+      <c r="I9">
+        <v>3.458541747201571</v>
+      </c>
+      <c r="J9">
+        <v>3.483328337998869</v>
+      </c>
+      <c r="K9">
+        <v>4.813569882290358</v>
+      </c>
+      <c r="L9">
+        <v>0.7096697947960776</v>
+      </c>
+      <c r="M9">
+        <v>1.156126342008376</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>1.958861904980206</v>
+      </c>
+      <c r="C10">
+        <v>8.225974922357942</v>
+      </c>
+      <c r="D10">
+        <v>1.588804929060806</v>
+      </c>
+      <c r="E10">
+        <v>4.874041378254197</v>
+      </c>
+      <c r="F10">
+        <v>1.63577847431798</v>
+      </c>
+      <c r="G10">
+        <v>1.015428947928249</v>
+      </c>
+      <c r="H10">
+        <v>2.195847213171828</v>
+      </c>
+      <c r="I10">
+        <v>3.940951158673476</v>
+      </c>
+      <c r="J10">
+        <v>3.828767196988058</v>
+      </c>
+      <c r="K10">
+        <v>6.213818437765056</v>
+      </c>
+      <c r="L10">
+        <v>0.9626500996606613</v>
+      </c>
+      <c r="M10">
+        <v>1.430416185621493</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>1.979815178819489</v>
+      </c>
+      <c r="C11">
+        <v>6.741508442756938</v>
+      </c>
+      <c r="D11">
+        <v>1.707128510353901</v>
+      </c>
+      <c r="E11">
+        <v>5.064559890619647</v>
+      </c>
+      <c r="F11">
+        <v>1.756455596764365</v>
+      </c>
+      <c r="G11">
+        <v>1.095781990591572</v>
+      </c>
+      <c r="H11">
+        <v>2.334638082983152</v>
+      </c>
+      <c r="I11">
+        <v>3.753475437329971</v>
+      </c>
+      <c r="J11">
+        <v>4.955764141795985</v>
+      </c>
+      <c r="K11">
+        <v>6.592301832569827</v>
+      </c>
+      <c r="L11">
+        <v>0.8596684569857418</v>
+      </c>
+      <c r="M11">
+        <v>1.395402036870331</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>1.944617853469676</v>
+      </c>
+      <c r="C12">
+        <v>6.198951502591198</v>
+      </c>
+      <c r="D12">
+        <v>1.46473977806212</v>
+      </c>
+      <c r="E12">
+        <v>4.575262527110037</v>
+      </c>
+      <c r="F12">
+        <v>1.504449199380579</v>
+      </c>
+      <c r="G12">
+        <v>0.9260184815406469</v>
+      </c>
+      <c r="H12">
+        <v>1.894998465357184</v>
+      </c>
+      <c r="I12">
+        <v>3.564682682401704</v>
+      </c>
+      <c r="J12">
+        <v>4.05355390012316</v>
+      </c>
+      <c r="K12">
+        <v>5.56996429634277</v>
+      </c>
+      <c r="L12">
+        <v>0.7607771082353829</v>
+      </c>
+      <c r="M12">
+        <v>1.18307550824296</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>1.841289926008275</v>
+      </c>
+      <c r="C13">
+        <v>7.201051051998762</v>
+      </c>
+      <c r="D13">
+        <v>1.531515610847452</v>
+      </c>
+      <c r="E13">
+        <v>4.821086774887509</v>
+      </c>
+      <c r="F13">
+        <v>1.585435925636496</v>
+      </c>
+      <c r="G13">
+        <v>0.9561656319515622</v>
+      </c>
+      <c r="H13">
+        <v>1.772368231121621</v>
+      </c>
+      <c r="I13">
+        <v>3.364440577859422</v>
+      </c>
+      <c r="J13">
+        <v>3.739794667225761</v>
+      </c>
+      <c r="K13">
+        <v>4.951547273627031</v>
+      </c>
+      <c r="L13">
+        <v>0.7132663716317986</v>
+      </c>
+      <c r="M13">
+        <v>1.27332107883046</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>1.702795472518328</v>
+      </c>
+      <c r="C14">
+        <v>5.831695903393473</v>
+      </c>
+      <c r="D14">
+        <v>1.504882961300219</v>
+      </c>
+      <c r="E14">
+        <v>4.026146835121498</v>
+      </c>
+      <c r="F14">
+        <v>1.181128338283655</v>
+      </c>
+      <c r="G14">
+        <v>0.9316906324653299</v>
+      </c>
+      <c r="H14">
+        <v>1.583277728037602</v>
+      </c>
+      <c r="I14">
+        <v>2.950793993238633</v>
+      </c>
+      <c r="J14">
+        <v>3.664690107327911</v>
+      </c>
+      <c r="K14">
+        <v>5.310771575203762</v>
+      </c>
+      <c r="L14">
+        <v>0.6975239629786576</v>
+      </c>
+      <c r="M14">
+        <v>1.144246451021685</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>0.9045656342424747</v>
+      </c>
+      <c r="C15">
+        <v>2.859925527163085</v>
+      </c>
+      <c r="D15">
+        <v>0.6379692883914083</v>
+      </c>
+      <c r="E15">
+        <v>2.249393408384412</v>
+      </c>
+      <c r="F15">
+        <v>0.802945293988511</v>
+      </c>
+      <c r="G15">
+        <v>0.473413702937625</v>
+      </c>
+      <c r="H15">
+        <v>0.9254915182038161</v>
+      </c>
+      <c r="I15">
+        <v>1.456814067186478</v>
+      </c>
+      <c r="J15">
+        <v>1.803231322638735</v>
+      </c>
+      <c r="K15">
+        <v>2.632876030072033</v>
+      </c>
+      <c r="L15">
+        <v>0.3864781788635187</v>
+      </c>
+      <c r="M15">
+        <v>0.5631242030042563</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>4.059863130783381</v>
+      </c>
+      <c r="C2">
+        <v>36.18573255192801</v>
+      </c>
+      <c r="D2">
+        <v>7.237901258935024</v>
+      </c>
+      <c r="E2">
+        <v>26.02544530087286</v>
+      </c>
+      <c r="F2">
+        <v>8.115475344088313</v>
+      </c>
+      <c r="G2">
+        <v>4.631057247068334</v>
+      </c>
+      <c r="H2">
+        <v>9.724253141976986</v>
+      </c>
+      <c r="I2">
+        <v>14.19546106079139</v>
+      </c>
+      <c r="J2">
+        <v>20.1384398073133</v>
+      </c>
+      <c r="K2">
+        <v>21.86440260705363</v>
+      </c>
+      <c r="L2">
+        <v>3.24460575231796</v>
+      </c>
+      <c r="M2">
+        <v>3.960427438933731</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>4.456184711391191</v>
+      </c>
+      <c r="C3">
+        <v>49.90586574359943</v>
+      </c>
+      <c r="D3">
+        <v>7.864138948003234</v>
+      </c>
+      <c r="E3">
+        <v>29.58538137703795</v>
+      </c>
+      <c r="F3">
+        <v>8.362225731481535</v>
+      </c>
+      <c r="G3">
+        <v>4.4388177720854</v>
+      </c>
+      <c r="H3">
+        <v>9.212961203342557</v>
+      </c>
+      <c r="I3">
+        <v>15.35971374221546</v>
+      </c>
+      <c r="J3">
+        <v>24.3021019727747</v>
+      </c>
+      <c r="K3">
+        <v>22.53193752272647</v>
+      </c>
+      <c r="L3">
+        <v>3.108374359499403</v>
+      </c>
+      <c r="M3">
+        <v>3.562312652292583</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>4.512773463553723</v>
+      </c>
+      <c r="C4">
+        <v>51.6836409473604</v>
+      </c>
+      <c r="D4">
+        <v>8.05777664229052</v>
+      </c>
+      <c r="E4">
+        <v>39.28249324753122</v>
+      </c>
+      <c r="F4">
+        <v>8.919022069548209</v>
+      </c>
+      <c r="G4">
+        <v>4.653303124749239</v>
+      </c>
+      <c r="H4">
+        <v>11.02072783578842</v>
+      </c>
+      <c r="I4">
+        <v>21.35839166799103</v>
+      </c>
+      <c r="J4">
+        <v>31.24505805462546</v>
+      </c>
+      <c r="K4">
+        <v>28.13176855112123</v>
+      </c>
+      <c r="L4">
+        <v>3.468991326474549</v>
+      </c>
+      <c r="M4">
+        <v>3.301116636262151</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>4.254624257834429</v>
+      </c>
+      <c r="C5">
+        <v>50.99827002543527</v>
+      </c>
+      <c r="D5">
+        <v>14.89962484436577</v>
+      </c>
+      <c r="E5">
+        <v>27.73063615717873</v>
+      </c>
+      <c r="F5">
+        <v>9.369940591565383</v>
+      </c>
+      <c r="G5">
+        <v>5.029769781447802</v>
+      </c>
+      <c r="H5">
+        <v>10.47002682371572</v>
+      </c>
+      <c r="I5">
+        <v>18.40489847064787</v>
+      </c>
+      <c r="J5">
+        <v>38.11389323874109</v>
+      </c>
+      <c r="K5">
+        <v>24.53436227803618</v>
+      </c>
+      <c r="L5">
+        <v>3.033759720794181</v>
+      </c>
+      <c r="M5">
+        <v>3.560869987474548</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>5.408548951371876</v>
+      </c>
+      <c r="C6">
+        <v>78.36934406985701</v>
+      </c>
+      <c r="D6">
+        <v>9.400001009141814</v>
+      </c>
+      <c r="E6">
+        <v>41.5105754978265</v>
+      </c>
+      <c r="F6">
+        <v>10.3850169308272</v>
+      </c>
+      <c r="G6">
+        <v>4.887257911731209</v>
+      </c>
+      <c r="H6">
+        <v>10.44575790572381</v>
+      </c>
+      <c r="I6">
+        <v>17.06256002737261</v>
+      </c>
+      <c r="J6">
+        <v>36.71626928241853</v>
+      </c>
+      <c r="K6">
+        <v>34.23990412062709</v>
+      </c>
+      <c r="L6">
+        <v>3.584475445105197</v>
+      </c>
+      <c r="M6">
+        <v>4.601226769810667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>5.086359868514235</v>
+      </c>
+      <c r="C7">
+        <v>104.2846320532687</v>
+      </c>
+      <c r="D7">
+        <v>7.892610588697628</v>
+      </c>
+      <c r="E7">
+        <v>39.77392162725822</v>
+      </c>
+      <c r="F7">
+        <v>10.87638387986763</v>
+      </c>
+      <c r="G7">
+        <v>5.392830102018797</v>
+      </c>
+      <c r="H7">
+        <v>8.508285734706956</v>
+      </c>
+      <c r="I7">
+        <v>14.71214369498658</v>
+      </c>
+      <c r="J7">
+        <v>22.98911703839407</v>
+      </c>
+      <c r="K7">
+        <v>20.43756021294822</v>
+      </c>
+      <c r="L7">
+        <v>3.410317674826491</v>
+      </c>
+      <c r="M7">
+        <v>4.058052412962532</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>4.575913610576653</v>
+      </c>
+      <c r="C8">
+        <v>47.37561941529971</v>
+      </c>
+      <c r="D8">
+        <v>7.321743436613263</v>
+      </c>
+      <c r="E8">
+        <v>28.19009401244594</v>
+      </c>
+      <c r="F8">
+        <v>9.203168363060067</v>
+      </c>
+      <c r="G8">
+        <v>4.882802295292732</v>
+      </c>
+      <c r="H8">
+        <v>8.663948293389556</v>
+      </c>
+      <c r="I8">
+        <v>14.92824840553305</v>
+      </c>
+      <c r="J8">
+        <v>34.39892381811901</v>
+      </c>
+      <c r="K8">
+        <v>22.78488900498766</v>
+      </c>
+      <c r="L8">
+        <v>2.881145084677367</v>
+      </c>
+      <c r="M8">
+        <v>4.221146737486448</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>4.950960688373843</v>
+      </c>
+      <c r="C9">
+        <v>48.07996233217762</v>
+      </c>
+      <c r="D9">
+        <v>9.369293494457013</v>
+      </c>
+      <c r="E9">
+        <v>51.88599621121307</v>
+      </c>
+      <c r="F9">
+        <v>10.27712430448128</v>
+      </c>
+      <c r="G9">
+        <v>5.301691906003475</v>
+      </c>
+      <c r="H9">
+        <v>8.919877978490314</v>
+      </c>
+      <c r="I9">
+        <v>17.94996001699316</v>
+      </c>
+      <c r="J9">
+        <v>23.88874008805884</v>
+      </c>
+      <c r="K9">
+        <v>27.32684516653704</v>
+      </c>
+      <c r="L9">
+        <v>2.855391272269095</v>
+      </c>
+      <c r="M9">
+        <v>3.717564929718125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>6.146995829409994</v>
+      </c>
+      <c r="C10">
+        <v>64.52361983893165</v>
+      </c>
+      <c r="D10">
+        <v>9.913677822534936</v>
+      </c>
+      <c r="E10">
+        <v>81.68128789155851</v>
+      </c>
+      <c r="F10">
+        <v>17.47966175507566</v>
+      </c>
+      <c r="G10">
+        <v>7.912987719511523</v>
+      </c>
+      <c r="H10">
+        <v>13.61053708206212</v>
+      </c>
+      <c r="I10">
+        <v>20.01479256264921</v>
+      </c>
+      <c r="J10">
+        <v>29.45627218982454</v>
+      </c>
+      <c r="K10">
+        <v>27.34608018029163</v>
+      </c>
+      <c r="L10">
+        <v>3.87389238256569</v>
+      </c>
+      <c r="M10">
+        <v>4.650123639125614</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>7.123709865915543</v>
+      </c>
+      <c r="C11">
+        <v>49.52071625682209</v>
+      </c>
+      <c r="D11">
+        <v>11.63204025256062</v>
+      </c>
+      <c r="E11">
+        <v>61.64573826271558</v>
+      </c>
+      <c r="F11">
+        <v>13.72352668543922</v>
+      </c>
+      <c r="G11">
+        <v>7.054900636484198</v>
+      </c>
+      <c r="H11">
+        <v>10.83334523077282</v>
+      </c>
+      <c r="I11">
+        <v>22.30445331147673</v>
+      </c>
+      <c r="J11">
+        <v>29.8691093967415</v>
+      </c>
+      <c r="K11">
+        <v>28.91691029973866</v>
+      </c>
+      <c r="L11">
+        <v>4.889166824120265</v>
+      </c>
+      <c r="M11">
+        <v>4.965948470093847</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>7.250413383394466</v>
+      </c>
+      <c r="C12">
+        <v>60.56846149745289</v>
+      </c>
+      <c r="D12">
+        <v>10.7910118192191</v>
+      </c>
+      <c r="E12">
+        <v>44.18003841220329</v>
+      </c>
+      <c r="F12">
+        <v>12.91083952686304</v>
+      </c>
+      <c r="G12">
+        <v>6.186333485876476</v>
+      </c>
+      <c r="H12">
+        <v>9.369056444178138</v>
+      </c>
+      <c r="I12">
+        <v>14.33547183529105</v>
+      </c>
+      <c r="J12">
+        <v>21.15937677769958</v>
+      </c>
+      <c r="K12">
+        <v>22.50918360903629</v>
+      </c>
+      <c r="L12">
+        <v>3.524922954997809</v>
+      </c>
+      <c r="M12">
+        <v>4.547992356513719</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>6.406983106636615</v>
+      </c>
+      <c r="C13">
+        <v>96.02121278630497</v>
+      </c>
+      <c r="D13">
+        <v>10.20984819025989</v>
+      </c>
+      <c r="E13">
+        <v>46.97601728566286</v>
+      </c>
+      <c r="F13">
+        <v>12.21798004759873</v>
+      </c>
+      <c r="G13">
+        <v>6.114261360457967</v>
+      </c>
+      <c r="H13">
+        <v>8.273625427212753</v>
+      </c>
+      <c r="I13">
+        <v>16.78805810303677</v>
+      </c>
+      <c r="J13">
+        <v>18.89125792556847</v>
+      </c>
+      <c r="K13">
+        <v>27.46612506041064</v>
+      </c>
+      <c r="L13">
+        <v>3.112184145273481</v>
+      </c>
+      <c r="M13">
+        <v>4.75574555962989</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>5.694916652141218</v>
+      </c>
+      <c r="C14">
+        <v>54.25583893339033</v>
+      </c>
+      <c r="D14">
+        <v>8.348433927152701</v>
+      </c>
+      <c r="E14">
+        <v>34.55305181719793</v>
+      </c>
+      <c r="F14">
+        <v>11.10854502738481</v>
+      </c>
+      <c r="G14">
+        <v>5.222502559670898</v>
+      </c>
+      <c r="H14">
+        <v>7.207470483101417</v>
+      </c>
+      <c r="I14">
+        <v>15.31623358897622</v>
+      </c>
+      <c r="J14">
+        <v>25.29672296696382</v>
+      </c>
+      <c r="K14">
+        <v>18.11044522699582</v>
+      </c>
+      <c r="L14">
+        <v>2.920094090937093</v>
+      </c>
+      <c r="M14">
+        <v>4.819951757678316</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2.930426977011205</v>
+      </c>
+      <c r="C15">
+        <v>36.73463897757834</v>
+      </c>
+      <c r="D15">
+        <v>5.749218696791174</v>
+      </c>
+      <c r="E15">
+        <v>33.4207311787026</v>
+      </c>
+      <c r="F15">
+        <v>5.53671367929988</v>
+      </c>
+      <c r="G15">
+        <v>3.327869045041671</v>
+      </c>
+      <c r="H15">
+        <v>4.28373242361655</v>
+      </c>
+      <c r="I15">
+        <v>8.027844021476463</v>
+      </c>
+      <c r="J15">
+        <v>11.70386834744208</v>
+      </c>
+      <c r="K15">
+        <v>9.938929847658766</v>
+      </c>
+      <c r="L15">
+        <v>1.557757617411191</v>
+      </c>
+      <c r="M15">
+        <v>2.49826722025525</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>4.492092511807615</v>
+      </c>
+      <c r="C2">
+        <v>40.01368302042479</v>
+      </c>
+      <c r="D2">
+        <v>8.571701561965645</v>
+      </c>
+      <c r="E2">
+        <v>28.51031301533897</v>
+      </c>
+      <c r="F2">
+        <v>8.93639338846166</v>
+      </c>
+      <c r="G2">
+        <v>5.229669377832169</v>
+      </c>
+      <c r="H2">
+        <v>10.39798790709522</v>
+      </c>
+      <c r="I2">
+        <v>15.49339093352479</v>
+      </c>
+      <c r="J2">
+        <v>23.40295900396184</v>
+      </c>
+      <c r="K2">
+        <v>23.43866016278162</v>
+      </c>
+      <c r="L2">
+        <v>3.717158915935268</v>
+      </c>
+      <c r="M2">
+        <v>4.251886293753512</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>4.918897857141927</v>
+      </c>
+      <c r="C3">
+        <v>53.58375536282697</v>
+      </c>
+      <c r="D3">
+        <v>8.743835684360867</v>
+      </c>
+      <c r="E3">
+        <v>32.92932076322173</v>
+      </c>
+      <c r="F3">
+        <v>10.66659869662422</v>
+      </c>
+      <c r="G3">
+        <v>5.36125177901086</v>
+      </c>
+      <c r="H3">
+        <v>9.989623998042067</v>
+      </c>
+      <c r="I3">
+        <v>17.25381716472012</v>
+      </c>
+      <c r="J3">
+        <v>24.69964002518831</v>
+      </c>
+      <c r="K3">
+        <v>25.92994165808681</v>
+      </c>
+      <c r="L3">
+        <v>3.668225128744571</v>
+      </c>
+      <c r="M3">
+        <v>3.838607004139023</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>5.058131110250899</v>
+      </c>
+      <c r="C4">
+        <v>61.63728985672238</v>
+      </c>
+      <c r="D4">
+        <v>8.946831562393742</v>
+      </c>
+      <c r="E4">
+        <v>44.04029700196073</v>
+      </c>
+      <c r="F4">
+        <v>9.796483975264744</v>
+      </c>
+      <c r="G4">
+        <v>5.550895340721362</v>
+      </c>
+      <c r="H4">
+        <v>11.91842730387769</v>
+      </c>
+      <c r="I4">
+        <v>39.59298644211017</v>
+      </c>
+      <c r="J4">
+        <v>34.09287620106893</v>
+      </c>
+      <c r="K4">
+        <v>30.23289690893845</v>
+      </c>
+      <c r="L4">
+        <v>3.605533697143904</v>
+      </c>
+      <c r="M4">
+        <v>3.406317436025092</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>5.029101910509449</v>
+      </c>
+      <c r="C5">
+        <v>53.51312726801902</v>
+      </c>
+      <c r="D5">
+        <v>12.35723942527865</v>
+      </c>
+      <c r="E5">
+        <v>33.06175095164849</v>
+      </c>
+      <c r="F5">
+        <v>10.99593432222137</v>
+      </c>
+      <c r="G5">
+        <v>5.487754874826761</v>
+      </c>
+      <c r="H5">
+        <v>12.06265515743659</v>
+      </c>
+      <c r="I5">
+        <v>22.80938686817856</v>
+      </c>
+      <c r="J5">
+        <v>39.95237793973855</v>
+      </c>
+      <c r="K5">
+        <v>27.61371061891656</v>
+      </c>
+      <c r="L5">
+        <v>3.600849356364903</v>
+      </c>
+      <c r="M5">
+        <v>3.866715216734959</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>5.689866289303238</v>
+      </c>
+      <c r="C6">
+        <v>94.83573914981882</v>
+      </c>
+      <c r="D6">
+        <v>9.538665101764051</v>
+      </c>
+      <c r="E6">
+        <v>49.35135457361289</v>
+      </c>
+      <c r="F6">
+        <v>12.13623130328289</v>
+      </c>
+      <c r="G6">
+        <v>5.674670719377591</v>
+      </c>
+      <c r="H6">
+        <v>10.39152103765723</v>
+      </c>
+      <c r="I6">
+        <v>24.94061927781581</v>
+      </c>
+      <c r="J6">
+        <v>33.13157709683888</v>
+      </c>
+      <c r="K6">
+        <v>30.58623707642459</v>
+      </c>
+      <c r="L6">
+        <v>4.018091704529857</v>
+      </c>
+      <c r="M6">
+        <v>4.991481916555285</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>5.606014375764952</v>
+      </c>
+      <c r="C7">
+        <v>104.2846320532687</v>
+      </c>
+      <c r="D7">
+        <v>8.931298984101463</v>
+      </c>
+      <c r="E7">
+        <v>39.75541492523889</v>
+      </c>
+      <c r="F7">
+        <v>12.31004972244459</v>
+      </c>
+      <c r="G7">
+        <v>5.623178822784276</v>
+      </c>
+      <c r="H7">
+        <v>10.67777664448757</v>
+      </c>
+      <c r="I7">
+        <v>16.83310695950629</v>
+      </c>
+      <c r="J7">
+        <v>22.96476931606498</v>
+      </c>
+      <c r="K7">
+        <v>21.77051780738274</v>
+      </c>
+      <c r="L7">
+        <v>3.792273454461526</v>
+      </c>
+      <c r="M7">
+        <v>4.319865368975295</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>4.984491711099794</v>
+      </c>
+      <c r="C8">
+        <v>49.42701172036979</v>
+      </c>
+      <c r="D8">
+        <v>8.332624798393086</v>
+      </c>
+      <c r="E8">
+        <v>39.64207136705289</v>
+      </c>
+      <c r="F8">
+        <v>10.6296470976006</v>
+      </c>
+      <c r="G8">
+        <v>5.651213027708482</v>
+      </c>
+      <c r="H8">
+        <v>9.676950758984544</v>
+      </c>
+      <c r="I8">
+        <v>19.05135937652802</v>
+      </c>
+      <c r="J8">
+        <v>39.38440314232446</v>
+      </c>
+      <c r="K8">
+        <v>31.17333294499889</v>
+      </c>
+      <c r="L8">
+        <v>3.329759763362078</v>
+      </c>
+      <c r="M8">
+        <v>4.662151006897863</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>5.287481770470878</v>
+      </c>
+      <c r="C9">
+        <v>55.5214316775406</v>
+      </c>
+      <c r="D9">
+        <v>12.77405578484473</v>
+      </c>
+      <c r="E9">
+        <v>71.74606365002585</v>
+      </c>
+      <c r="F9">
+        <v>12.92943327655416</v>
+      </c>
+      <c r="G9">
+        <v>5.675263086855168</v>
+      </c>
+      <c r="H9">
+        <v>10.6685650220267</v>
+      </c>
+      <c r="I9">
+        <v>19.490025762307</v>
+      </c>
+      <c r="J9">
+        <v>26.55998449633026</v>
+      </c>
+      <c r="K9">
+        <v>32.23723772008246</v>
+      </c>
+      <c r="L9">
+        <v>3.159801571049323</v>
+      </c>
+      <c r="M9">
+        <v>4.115020371920123</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>7.217968530013056</v>
+      </c>
+      <c r="C10">
+        <v>70.06628679983895</v>
+      </c>
+      <c r="D10">
+        <v>11.31336915874272</v>
+      </c>
+      <c r="E10">
+        <v>85.09057203798621</v>
+      </c>
+      <c r="F10">
+        <v>25.85967562673568</v>
+      </c>
+      <c r="G10">
+        <v>8.981035491238798</v>
+      </c>
+      <c r="H10">
+        <v>14.92886764458343</v>
+      </c>
+      <c r="I10">
+        <v>21.61204690957359</v>
+      </c>
+      <c r="J10">
+        <v>30.05389862011868</v>
+      </c>
+      <c r="K10">
+        <v>26.97650835014687</v>
+      </c>
+      <c r="L10">
+        <v>5.062531052690753</v>
+      </c>
+      <c r="M10">
+        <v>4.955301404208411</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>8.056961567714012</v>
+      </c>
+      <c r="C11">
+        <v>52.03466914524306</v>
+      </c>
+      <c r="D11">
+        <v>12.69682213825984</v>
+      </c>
+      <c r="E11">
+        <v>65.45108040607579</v>
+      </c>
+      <c r="F11">
+        <v>13.03351622692987</v>
+      </c>
+      <c r="G11">
+        <v>9.521459776881812</v>
+      </c>
+      <c r="H11">
+        <v>13.40588659645215</v>
+      </c>
+      <c r="I11">
+        <v>24.9238940162734</v>
+      </c>
+      <c r="J11">
+        <v>33.73295847501409</v>
+      </c>
+      <c r="K11">
+        <v>34.08872863649473</v>
+      </c>
+      <c r="L11">
+        <v>5.203997835165775</v>
+      </c>
+      <c r="M11">
+        <v>5.284569893589095</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>7.565085250097002</v>
+      </c>
+      <c r="C12">
+        <v>56.3250116660894</v>
+      </c>
+      <c r="D12">
+        <v>14.42768447433914</v>
+      </c>
+      <c r="E12">
+        <v>53.61960437147341</v>
+      </c>
+      <c r="F12">
+        <v>13.53251623657362</v>
+      </c>
+      <c r="G12">
+        <v>7.060847350341315</v>
+      </c>
+      <c r="H12">
+        <v>10.55927827258207</v>
+      </c>
+      <c r="I12">
+        <v>16.64578996901918</v>
+      </c>
+      <c r="J12">
+        <v>24.07805410409969</v>
+      </c>
+      <c r="K12">
+        <v>25.28305041811591</v>
+      </c>
+      <c r="L12">
+        <v>4.143553779921012</v>
+      </c>
+      <c r="M12">
+        <v>5.081344572914241</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>6.522211796233711</v>
+      </c>
+      <c r="C13">
+        <v>100.3198716657155</v>
+      </c>
+      <c r="D13">
+        <v>15.50593083312338</v>
+      </c>
+      <c r="E13">
+        <v>57.12602584664103</v>
+      </c>
+      <c r="F13">
+        <v>14.35979951340064</v>
+      </c>
+      <c r="G13">
+        <v>7.022905514510799</v>
+      </c>
+      <c r="H13">
+        <v>8.644560839633092</v>
+      </c>
+      <c r="I13">
+        <v>17.83802058438342</v>
+      </c>
+      <c r="J13">
+        <v>22.54474920056573</v>
+      </c>
+      <c r="K13">
+        <v>29.38765668599693</v>
+      </c>
+      <c r="L13">
+        <v>3.907877720859591</v>
+      </c>
+      <c r="M13">
+        <v>4.901635130115908</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>6.345468937315263</v>
+      </c>
+      <c r="C14">
+        <v>52.91306685205372</v>
+      </c>
+      <c r="D14">
+        <v>9.961322375320306</v>
+      </c>
+      <c r="E14">
+        <v>40.00466526822849</v>
+      </c>
+      <c r="F14">
+        <v>12.60952182286766</v>
+      </c>
+      <c r="G14">
+        <v>6.072151758758413</v>
+      </c>
+      <c r="H14">
+        <v>8.319811323789924</v>
+      </c>
+      <c r="I14">
+        <v>16.42621395810422</v>
+      </c>
+      <c r="J14">
+        <v>27.73810831133213</v>
+      </c>
+      <c r="K14">
+        <v>25.93222085458164</v>
+      </c>
+      <c r="L14">
+        <v>3.093098338976354</v>
+      </c>
+      <c r="M14">
+        <v>5.043890718477585</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>3.402830659205338</v>
+      </c>
+      <c r="C15">
+        <v>36.34445454249064</v>
+      </c>
+      <c r="D15">
+        <v>8.950636552235839</v>
+      </c>
+      <c r="E15">
+        <v>33.38993001966375</v>
+      </c>
+      <c r="F15">
+        <v>6.162371086775511</v>
+      </c>
+      <c r="G15">
+        <v>3.715142888987211</v>
+      </c>
+      <c r="H15">
+        <v>5.498355381102868</v>
+      </c>
+      <c r="I15">
+        <v>8.990989284410613</v>
+      </c>
+      <c r="J15">
+        <v>14.69840145252728</v>
+      </c>
+      <c r="K15">
+        <v>12.10787057418992</v>
+      </c>
+      <c r="L15">
+        <v>1.747755610813695</v>
+      </c>
+      <c r="M15">
+        <v>2.771068401953933</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PERÍODO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Agropecuária</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria extrativa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Indústria de transformação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades imobiliárias</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Outras atividades de serviços</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B2">
         <v>4.847560272998242</v>
       </c>
       <c r="C2">
@@ -4260,40 +8289,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.229509306061297</v>
+        <v>10131169.06987146</v>
       </c>
       <c r="C2">
-        <v>5.422895149107467</v>
+        <v>525347.74654318</v>
       </c>
       <c r="D2">
-        <v>1.132517873130095</v>
+        <v>11666775.39184005</v>
       </c>
       <c r="E2">
-        <v>3.48050920527917</v>
+        <v>780849.16936122</v>
       </c>
       <c r="F2">
-        <v>1.16087179542573</v>
+        <v>7601504.93678521</v>
       </c>
       <c r="G2">
-        <v>0.8026298210845056</v>
+        <v>17008188.874753</v>
       </c>
       <c r="H2">
-        <v>1.530397174176123</v>
+        <v>4237602.11258804</v>
       </c>
       <c r="I2">
-        <v>3.634789800402286</v>
+        <v>1238319.60038592</v>
       </c>
       <c r="J2">
-        <v>3.485185464514529</v>
+        <v>1227529.30438389</v>
       </c>
       <c r="K2">
-        <v>4.559033770657147</v>
+        <v>539938.51657356</v>
       </c>
       <c r="L2">
-        <v>0.5720107879756813</v>
+        <v>24287152.37666379</v>
       </c>
       <c r="M2">
-        <v>1.075411208719432</v>
+        <v>9961477.01362006</v>
       </c>
     </row>
     <row r="3">
@@ -4303,40 +8332,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.145909126694403</v>
+        <v>10011095.31897503</v>
       </c>
       <c r="C3">
-        <v>5.600027380663285</v>
+        <v>541689.19456019</v>
       </c>
       <c r="D3">
-        <v>1.1544791780968</v>
+        <v>11374432.52112467</v>
       </c>
       <c r="E3">
-        <v>3.313489361712263</v>
+        <v>908663.28932691</v>
       </c>
       <c r="F3">
-        <v>1.107356488965733</v>
+        <v>8084246.48189599</v>
       </c>
       <c r="G3">
-        <v>0.7556625881647681</v>
+        <v>17350052.70136382</v>
       </c>
       <c r="H3">
-        <v>1.662705434518929</v>
+        <v>4196673.6604753</v>
       </c>
       <c r="I3">
-        <v>3.343277578646285</v>
+        <v>1291836.25918293</v>
       </c>
       <c r="J3">
-        <v>3.067822707257595</v>
+        <v>1287728.34425066</v>
       </c>
       <c r="K3">
-        <v>4.268825398506164</v>
+        <v>546002.92156694</v>
       </c>
       <c r="L3">
-        <v>0.5576023476828285</v>
+        <v>25248785.45482136</v>
       </c>
       <c r="M3">
-        <v>1.114799324266599</v>
+        <v>9955452.74718361</v>
       </c>
     </row>
     <row r="4">
@@ -4346,40 +8375,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.289928248091808</v>
+        <v>9442806.033169139</v>
       </c>
       <c r="C4">
-        <v>4.684193230397252</v>
+        <v>472136.02881972</v>
       </c>
       <c r="D4">
-        <v>1.271465392402865</v>
+        <v>11994864.60557445</v>
       </c>
       <c r="E4">
-        <v>3.422182276402452</v>
+        <v>927328.56936573</v>
       </c>
       <c r="F4">
-        <v>1.349662438642522</v>
+        <v>7847560.27364031</v>
       </c>
       <c r="G4">
-        <v>0.8145465260978322</v>
+        <v>17396875.89463785</v>
       </c>
       <c r="H4">
-        <v>1.704634590636747</v>
+        <v>4351706.29095564</v>
       </c>
       <c r="I4">
-        <v>3.26803690089042</v>
+        <v>1282524.07861221</v>
       </c>
       <c r="J4">
-        <v>3.581326736320688</v>
+        <v>1321247.32698534</v>
       </c>
       <c r="K4">
-        <v>5.309476692836358</v>
+        <v>569435.69673629</v>
       </c>
       <c r="L4">
-        <v>0.627884114225734</v>
+        <v>25801072.45869324</v>
       </c>
       <c r="M4">
-        <v>1.117192123712726</v>
+        <v>10185559.32940984</v>
       </c>
     </row>
     <row r="5">
@@ -4389,40 +8418,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.245579554740835</v>
+        <v>9220138.25684805</v>
       </c>
       <c r="C5">
-        <v>5.916611759372524</v>
+        <v>483357.97659423</v>
       </c>
       <c r="D5">
-        <v>1.235992549751658</v>
+        <v>11520912.25963946</v>
       </c>
       <c r="E5">
-        <v>3.41474354148054</v>
+        <v>877587.3195666</v>
       </c>
       <c r="F5">
-        <v>1.407216410652225</v>
+        <v>7695776.00565686</v>
       </c>
       <c r="G5">
-        <v>0.8013147417887808</v>
+        <v>17617119.91895033</v>
       </c>
       <c r="H5">
-        <v>1.631364805663721</v>
+        <v>4317521.80763089</v>
       </c>
       <c r="I5">
-        <v>3.060597517936308</v>
+        <v>1208897.27824553</v>
       </c>
       <c r="J5">
-        <v>3.182892098083798</v>
+        <v>1258330.26363626</v>
       </c>
       <c r="K5">
-        <v>5.013767820466216</v>
+        <v>610702.69322432</v>
       </c>
       <c r="L5">
-        <v>0.6176146613340081</v>
+        <v>26579145.42190388</v>
       </c>
       <c r="M5">
-        <v>1.018165437043274</v>
+        <v>10235753.13480167</v>
       </c>
     </row>
     <row r="6">
@@ -4432,40 +8461,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.36690774103845</v>
+        <v>8891547.18605167</v>
       </c>
       <c r="C6">
-        <v>6.06591524225312</v>
+        <v>438066.66671524</v>
       </c>
       <c r="D6">
-        <v>1.417790824902772</v>
+        <v>10320012.70736799</v>
       </c>
       <c r="E6">
-        <v>5.096847185389179</v>
+        <v>759312.8315444</v>
       </c>
       <c r="F6">
-        <v>1.383345398251238</v>
+        <v>7455723.42978543</v>
       </c>
       <c r="G6">
-        <v>0.8336520026707435</v>
+        <v>17411451.04678764</v>
       </c>
       <c r="H6">
-        <v>1.843682935078834</v>
+        <v>4603824.54814548</v>
       </c>
       <c r="I6">
-        <v>3.485078902382059</v>
+        <v>1256639.87949631</v>
       </c>
       <c r="J6">
-        <v>5.082178678255985</v>
+        <v>1260154.89485871</v>
       </c>
       <c r="K6">
-        <v>4.625380152230658</v>
+        <v>518113.13265651</v>
       </c>
       <c r="L6">
-        <v>0.7287056942710369</v>
+        <v>26898858.5829326</v>
       </c>
       <c r="M6">
-        <v>1.180518958176392</v>
+        <v>10070811.58912805</v>
       </c>
     </row>
     <row r="7">
@@ -4475,40 +8504,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.57842999874379</v>
+        <v>8517282.68212196</v>
       </c>
       <c r="C7">
-        <v>5.557745595622676</v>
+        <v>406143.8839813</v>
       </c>
       <c r="D7">
-        <v>1.26933219910818</v>
+        <v>10564060.73381221</v>
       </c>
       <c r="E7">
-        <v>4.045237745523112</v>
+        <v>880835.31724384</v>
       </c>
       <c r="F7">
-        <v>1.381736865000149</v>
+        <v>7086568.29041464</v>
       </c>
       <c r="G7">
-        <v>0.8667098488719912</v>
+        <v>17470873.21370806</v>
       </c>
       <c r="H7">
-        <v>1.612149727079564</v>
+        <v>4528253.82291903</v>
       </c>
       <c r="I7">
-        <v>3.598827662304359</v>
+        <v>1208859.80415367</v>
       </c>
       <c r="J7">
-        <v>3.903767301729239</v>
+        <v>1209737.41740583</v>
       </c>
       <c r="K7">
-        <v>4.347414711761307</v>
+        <v>561667.43195191</v>
       </c>
       <c r="L7">
-        <v>0.6656510678540066</v>
+        <v>27550319.42380237</v>
       </c>
       <c r="M7">
-        <v>1.048312678150514</v>
+        <v>10130055.916907</v>
       </c>
     </row>
     <row r="8">
@@ -4518,40 +8547,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.303883805551855</v>
+        <v>8457512.500733869</v>
       </c>
       <c r="C8">
-        <v>6.067357533031254</v>
+        <v>444966.10945317</v>
       </c>
       <c r="D8">
-        <v>1.403372048619912</v>
+        <v>10622575.19224855</v>
       </c>
       <c r="E8">
-        <v>4.057611668795655</v>
+        <v>835991.16454865</v>
       </c>
       <c r="F8">
-        <v>1.213744574905402</v>
+        <v>6808013.44804323</v>
       </c>
       <c r="G8">
-        <v>0.8442317228751375</v>
+        <v>17646800.94937814</v>
       </c>
       <c r="H8">
-        <v>1.620853768828055</v>
+        <v>4664998.21097053</v>
       </c>
       <c r="I8">
-        <v>3.332152888587812</v>
+        <v>1255462.10573991</v>
       </c>
       <c r="J8">
-        <v>3.614013788234624</v>
+        <v>1252229.08201061</v>
       </c>
       <c r="K8">
-        <v>4.964861376404981</v>
+        <v>617846.6250033</v>
       </c>
       <c r="L8">
-        <v>0.6217800534006352</v>
+        <v>28415143.98556478</v>
       </c>
       <c r="M8">
-        <v>1.061189345053169</v>
+        <v>10452185.46600144</v>
       </c>
     </row>
     <row r="9">
@@ -4561,40 +8590,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.51241940713255</v>
+        <v>8552125.98846348</v>
       </c>
       <c r="C9">
-        <v>4.924461460619824</v>
+        <v>415709.1077443</v>
       </c>
       <c r="D9">
-        <v>1.179607521473681</v>
+        <v>10948345.9828455</v>
       </c>
       <c r="E9">
-        <v>4.082277459013457</v>
+        <v>892215.6781981</v>
       </c>
       <c r="F9">
-        <v>1.284583405392732</v>
+        <v>6858714.60800785</v>
       </c>
       <c r="G9">
-        <v>0.857982131618952</v>
+        <v>17864860.7838765</v>
       </c>
       <c r="H9">
-        <v>1.5277165853577</v>
+        <v>4804140.8508037</v>
       </c>
       <c r="I9">
-        <v>3.290042847848384</v>
+        <v>1348807.77935802</v>
       </c>
       <c r="J9">
-        <v>3.277534660268102</v>
+        <v>1256166.01357635</v>
       </c>
       <c r="K9">
-        <v>4.47913374434104</v>
+        <v>525252.87257617</v>
       </c>
       <c r="L9">
-        <v>0.623405736057393</v>
+        <v>29607698.48863239</v>
       </c>
       <c r="M9">
-        <v>1.113967901304608</v>
+        <v>10420038.64747221</v>
       </c>
     </row>
     <row r="10">
@@ -4604,40 +8633,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.770448501411388</v>
+        <v>7955073.86936484</v>
       </c>
       <c r="C10">
-        <v>7.922132798221261</v>
+        <v>439334.45457577</v>
       </c>
       <c r="D10">
-        <v>1.432295248209979</v>
+        <v>10020635.75123525</v>
       </c>
       <c r="E10">
-        <v>4.511625670624748</v>
+        <v>745603.89052575</v>
       </c>
       <c r="F10">
-        <v>1.494292874704401</v>
+        <v>6150876.83269391</v>
       </c>
       <c r="G10">
-        <v>0.9218973301385383</v>
+        <v>16441313.07232997</v>
       </c>
       <c r="H10">
-        <v>1.970170568040978</v>
+        <v>4559947.94786841</v>
       </c>
       <c r="I10">
-        <v>3.851741525271372</v>
+        <v>1300669.77013141</v>
       </c>
       <c r="J10">
-        <v>3.571980518068966</v>
+        <v>1231219.76847468</v>
       </c>
       <c r="K10">
-        <v>5.819594722840173</v>
+        <v>506669.48265081</v>
       </c>
       <c r="L10">
-        <v>0.7850082761908487</v>
+        <v>25591771.00905569</v>
       </c>
       <c r="M10">
-        <v>1.256948504275537</v>
+        <v>10317915.53959142</v>
       </c>
     </row>
     <row r="11">
@@ -4647,40 +8676,40 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.756787229900745</v>
+        <v>8717731.854640869</v>
       </c>
       <c r="C11">
-        <v>6.842685300827355</v>
+        <v>430877.44054901</v>
       </c>
       <c r="D11">
-        <v>1.659444269398046</v>
+        <v>10408117.04851821</v>
       </c>
       <c r="E11">
-        <v>4.820188068413774</v>
+        <v>631554.10671841</v>
       </c>
       <c r="F11">
-        <v>1.691186809373708</v>
+        <v>6739690.28413482</v>
       </c>
       <c r="G11">
-        <v>1.01260330005212</v>
+        <v>16688815.1882241</v>
       </c>
       <c r="H11">
-        <v>2.086724149174064</v>
+        <v>4486068.38350159</v>
       </c>
       <c r="I11">
-        <v>3.59522377877838</v>
+        <v>1454613.47838881</v>
       </c>
       <c r="J11">
-        <v>4.60873951191647</v>
+        <v>1307079.85646931</v>
       </c>
       <c r="K11">
-        <v>6.265700312288332</v>
+        <v>599769.0130365</v>
       </c>
       <c r="L11">
-        <v>0.8007165448416614</v>
+        <v>26165899.8318212</v>
       </c>
       <c r="M11">
-        <v>1.359065990292055</v>
+        <v>10264757.10360347</v>
       </c>
     </row>
     <row r="12">
@@ -4690,40 +8719,40 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.972930386400396</v>
+        <v>8434224.244372969</v>
       </c>
       <c r="C12">
-        <v>5.908265861290106</v>
+        <v>481752.54050793</v>
       </c>
       <c r="D12">
-        <v>1.346142466789208</v>
+        <v>10950637.43420228</v>
       </c>
       <c r="E12">
-        <v>4.473131116686156</v>
+        <v>698271.96275118</v>
       </c>
       <c r="F12">
-        <v>1.470576736620326</v>
+        <v>7121321.49904569</v>
       </c>
       <c r="G12">
-        <v>0.899481591222253</v>
+        <v>18286822.91346958</v>
       </c>
       <c r="H12">
-        <v>1.706510729568999</v>
+        <v>5107516.87572326</v>
       </c>
       <c r="I12">
-        <v>3.340128457392646</v>
+        <v>1665927.06010485</v>
       </c>
       <c r="J12">
-        <v>3.826703262115062</v>
+        <v>1475231.17109457</v>
       </c>
       <c r="K12">
-        <v>5.247752198612668</v>
+        <v>594265.0207214101</v>
       </c>
       <c r="L12">
-        <v>0.6707843710798715</v>
+        <v>29462230.18861698</v>
       </c>
       <c r="M12">
-        <v>1.078536333383202</v>
+        <v>10843395.51059305</v>
       </c>
     </row>
     <row r="13">
@@ -4733,40 +8762,40 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.656838535675915</v>
+        <v>8066796.93647456</v>
       </c>
       <c r="C13">
-        <v>7.054917103522541</v>
+        <v>528389.95442901</v>
       </c>
       <c r="D13">
-        <v>1.434872988288003</v>
+        <v>11452626.92623697</v>
       </c>
       <c r="E13">
-        <v>4.861737091937679</v>
+        <v>719303.68249267</v>
       </c>
       <c r="F13">
-        <v>1.490415948086583</v>
+        <v>7286492.07623505</v>
       </c>
       <c r="G13">
-        <v>0.8900361303720983</v>
+        <v>18666178.11462046</v>
       </c>
       <c r="H13">
-        <v>1.71408683243416</v>
+        <v>5376650.45853045</v>
       </c>
       <c r="I13">
-        <v>3.196475143018311</v>
+        <v>1764591.41153428</v>
       </c>
       <c r="J13">
-        <v>3.528636029218449</v>
+        <v>1533525.51074562</v>
       </c>
       <c r="K13">
-        <v>4.71258680424362</v>
+        <v>666604.01794775</v>
       </c>
       <c r="L13">
-        <v>0.5963896972469169</v>
+        <v>31424668.64863402</v>
       </c>
       <c r="M13">
-        <v>1.19136228413636</v>
+        <v>11202148.35399749</v>
       </c>
     </row>
     <row r="14">
@@ -4776,40 +8805,40 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.573054290823048</v>
+        <v>7789844.78269371</v>
       </c>
       <c r="C14">
-        <v>5.775015592394986</v>
+        <v>541239.73234154</v>
       </c>
       <c r="D14">
-        <v>1.448052037880141</v>
+        <v>11728299.5826466</v>
       </c>
       <c r="E14">
-        <v>3.893389754353624</v>
+        <v>751626.19462474</v>
       </c>
       <c r="F14">
-        <v>1.136727461094893</v>
+        <v>7674501.30312161</v>
       </c>
       <c r="G14">
-        <v>0.8512893678858247</v>
+        <v>19415398.50524363</v>
       </c>
       <c r="H14">
-        <v>1.490994169233142</v>
+        <v>5792188.08111072</v>
       </c>
       <c r="I14">
-        <v>2.812658987198598</v>
+        <v>1699731.16485368</v>
       </c>
       <c r="J14">
-        <v>3.559050133612009</v>
+        <v>1536224.5660204</v>
       </c>
       <c r="K14">
-        <v>4.937871702839121</v>
+        <v>731931.03568128</v>
       </c>
       <c r="L14">
-        <v>0.6100656000659873</v>
+        <v>31979393.03450106</v>
       </c>
       <c r="M14">
-        <v>1.083759406392644</v>
+        <v>11642568.05739504</v>
       </c>
     </row>
     <row r="15">
@@ -4819,40 +8848,40 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.8219250263801855</v>
+        <v>23258759.02318826</v>
       </c>
       <c r="C15">
-        <v>2.828888800341245</v>
+        <v>1774876.84250874</v>
       </c>
       <c r="D15">
-        <v>0.6124977714940172</v>
+        <v>35633855.37325487</v>
       </c>
       <c r="E15">
-        <v>2.161028073972597</v>
+        <v>2269266.53887683</v>
       </c>
       <c r="F15">
-        <v>0.7518038954981799</v>
+        <v>22141080.08462092</v>
       </c>
       <c r="G15">
-        <v>0.4221341049249467</v>
+        <v>57908836.23791794</v>
       </c>
       <c r="H15">
-        <v>0.8895251141264583</v>
+        <v>17694614.74814179</v>
       </c>
       <c r="I15">
-        <v>1.429619085615528</v>
+        <v>5280661.02597962</v>
       </c>
       <c r="J15">
-        <v>1.664082672826958</v>
+        <v>4871733.14801245</v>
       </c>
       <c r="K15">
-        <v>2.478289220100647</v>
+        <v>2259798.25370441</v>
       </c>
       <c r="L15">
-        <v>0.3423464876062325</v>
+        <v>96526837.34105805</v>
       </c>
       <c r="M15">
-        <v>0.5490223231706377</v>
+        <v>35554549.51039481</v>
       </c>
     </row>
   </sheetData>
@@ -4939,40 +8968,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.314362904276624</v>
+        <v>396342644.0281553</v>
       </c>
       <c r="C2">
-        <v>5.624013373672638</v>
+        <v>23944303.11046864</v>
       </c>
       <c r="D2">
-        <v>1.185261311493225</v>
+        <v>483786860.718093</v>
       </c>
       <c r="E2">
-        <v>3.640733733499985</v>
+        <v>32600093.49937929</v>
       </c>
       <c r="F2">
-        <v>1.194570504447914</v>
+        <v>317136005.0591235</v>
       </c>
       <c r="G2">
-        <v>0.8565255809558048</v>
+        <v>742132045.430328</v>
       </c>
       <c r="H2">
-        <v>1.662252503360129</v>
+        <v>196420154.6606708</v>
       </c>
       <c r="I2">
-        <v>3.674858805236258</v>
+        <v>50302307.81583586</v>
       </c>
       <c r="J2">
-        <v>3.613502185656624</v>
+        <v>46746836.18013324</v>
       </c>
       <c r="K2">
-        <v>4.837207260812677</v>
+        <v>22259414.55783131</v>
       </c>
       <c r="L2">
-        <v>0.656422943442294</v>
+        <v>933419756.5220565</v>
       </c>
       <c r="M2">
-        <v>1.110160418304029</v>
+        <v>360184388.0913892</v>
       </c>
     </row>
     <row r="3">
@@ -4982,40 +9011,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.209365973696709</v>
+        <v>384253334.2422557</v>
       </c>
       <c r="C3">
-        <v>5.864605027722864</v>
+        <v>24758558.02960905</v>
       </c>
       <c r="D3">
-        <v>1.199130166701676</v>
+        <v>469332048.2280596</v>
       </c>
       <c r="E3">
-        <v>3.428093625864266</v>
+        <v>36600437.72358084</v>
       </c>
       <c r="F3">
-        <v>1.144230160552132</v>
+        <v>336630888.0835547</v>
       </c>
       <c r="G3">
-        <v>0.7889672856494976</v>
+        <v>749235964.3401207</v>
       </c>
       <c r="H3">
-        <v>1.712039266091775</v>
+        <v>189445380.7509479</v>
       </c>
       <c r="I3">
-        <v>3.625167657681468</v>
+        <v>52876986.98527918</v>
       </c>
       <c r="J3">
-        <v>3.135811199746726</v>
+        <v>49820544.13274872</v>
       </c>
       <c r="K3">
-        <v>4.633584072734922</v>
+        <v>22214364.586193</v>
       </c>
       <c r="L3">
-        <v>0.6357284122973624</v>
+        <v>965398708.5080655</v>
       </c>
       <c r="M3">
-        <v>1.153462473577575</v>
+        <v>358620835.5316415</v>
       </c>
     </row>
     <row r="4">
@@ -5025,40 +9054,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.358847473116001</v>
+        <v>356495915.3376368</v>
       </c>
       <c r="C4">
-        <v>4.608659910007755</v>
+        <v>21166256.79964536</v>
       </c>
       <c r="D4">
-        <v>1.28594618532278</v>
+        <v>494115705.3643463</v>
       </c>
       <c r="E4">
-        <v>3.559617464309491</v>
+        <v>37794982.26003975</v>
       </c>
       <c r="F4">
-        <v>1.356986461902464</v>
+        <v>324787050.3787562</v>
       </c>
       <c r="G4">
-        <v>0.8254632641116486</v>
+        <v>746648954.8425741</v>
       </c>
       <c r="H4">
-        <v>1.728551864759313</v>
+        <v>194095260.0841012</v>
       </c>
       <c r="I4">
-        <v>3.455468827521229</v>
+        <v>52290898.21916119</v>
       </c>
       <c r="J4">
-        <v>3.610989419289638</v>
+        <v>50479025.97816577</v>
       </c>
       <c r="K4">
-        <v>5.828042273809888</v>
+        <v>23733225.27371601</v>
       </c>
       <c r="L4">
-        <v>0.6918545988700235</v>
+        <v>982584797.315042</v>
       </c>
       <c r="M4">
-        <v>1.168985166637366</v>
+        <v>366638586.8058777</v>
       </c>
     </row>
     <row r="5">
@@ -5068,40 +9097,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.295786108582208</v>
+        <v>344445248.7505562</v>
       </c>
       <c r="C5">
-        <v>5.781807814151331</v>
+        <v>21173182.43649637</v>
       </c>
       <c r="D5">
-        <v>1.304699055190227</v>
+        <v>469230970.7683679</v>
       </c>
       <c r="E5">
-        <v>3.676838558459818</v>
+        <v>35723630.54434889</v>
       </c>
       <c r="F5">
-        <v>1.452628989414401</v>
+        <v>313307131.3530088</v>
       </c>
       <c r="G5">
-        <v>0.8443945556070273</v>
+        <v>746806798.7009894</v>
       </c>
       <c r="H5">
-        <v>1.710679608013757</v>
+        <v>190888556.2496537</v>
       </c>
       <c r="I5">
-        <v>3.186937776499812</v>
+        <v>48910437.09189928</v>
       </c>
       <c r="J5">
-        <v>3.322618485857675</v>
+        <v>47802528.98456981</v>
       </c>
       <c r="K5">
-        <v>5.060266596289079</v>
+        <v>24824714.4955059</v>
       </c>
       <c r="L5">
-        <v>0.6985459937766789</v>
+        <v>1002931033.802408</v>
       </c>
       <c r="M5">
-        <v>1.082412442624864</v>
+        <v>368989733.9773757</v>
       </c>
     </row>
     <row r="6">
@@ -5111,40 +9140,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.452558082071599</v>
+        <v>336449742.7856086</v>
       </c>
       <c r="C6">
-        <v>5.997073175351049</v>
+        <v>19164401.49173496</v>
       </c>
       <c r="D6">
-        <v>1.440568486417168</v>
+        <v>420327412.1092491</v>
       </c>
       <c r="E6">
-        <v>5.305866218884682</v>
+        <v>30454666.97753678</v>
       </c>
       <c r="F6">
-        <v>1.437828280894304</v>
+        <v>301206675.7052776</v>
       </c>
       <c r="G6">
-        <v>0.8856491432736457</v>
+        <v>726758325.7256581</v>
       </c>
       <c r="H6">
-        <v>1.83648067475091</v>
+        <v>198716682.8650804</v>
       </c>
       <c r="I6">
-        <v>3.532400159055796</v>
+        <v>51045055.610378</v>
       </c>
       <c r="J6">
-        <v>5.251337622969313</v>
+        <v>49058528.89086418</v>
       </c>
       <c r="K6">
-        <v>4.853203324395947</v>
+        <v>21197179.46812446</v>
       </c>
       <c r="L6">
-        <v>0.7663323393924406</v>
+        <v>1008160625.388953</v>
       </c>
       <c r="M6">
-        <v>1.200736138632501</v>
+        <v>368549501.7069538</v>
       </c>
     </row>
     <row r="7">
@@ -5154,40 +9183,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.723286455445459</v>
+        <v>324863000.4964049</v>
       </c>
       <c r="C7">
-        <v>5.537053082648635</v>
+        <v>17100051.39665658</v>
       </c>
       <c r="D7">
-        <v>1.322496640906426</v>
+        <v>427203217.7269363</v>
       </c>
       <c r="E7">
-        <v>3.862628375052267</v>
+        <v>34491344.81693556</v>
       </c>
       <c r="F7">
-        <v>1.404933544316567</v>
+        <v>282058408.0946261</v>
       </c>
       <c r="G7">
-        <v>0.8914392741006216</v>
+        <v>724554161.429369</v>
       </c>
       <c r="H7">
-        <v>1.668134473785199</v>
+        <v>195515227.6562069</v>
       </c>
       <c r="I7">
-        <v>3.740862104781189</v>
+        <v>49205039.16551208</v>
       </c>
       <c r="J7">
-        <v>3.959094880669738</v>
+        <v>47347434.60415666</v>
       </c>
       <c r="K7">
-        <v>4.482010031351503</v>
+        <v>22312466.39591103</v>
       </c>
       <c r="L7">
-        <v>0.7309274083309352</v>
+        <v>1023168989.161571</v>
       </c>
       <c r="M7">
-        <v>1.090482662017584</v>
+        <v>370206263.0837951</v>
       </c>
     </row>
     <row r="8">
@@ -5197,40 +9226,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.401826221762044</v>
+        <v>321334320.5389965</v>
       </c>
       <c r="C8">
-        <v>6.10029947942409</v>
+        <v>19211333.27595111</v>
       </c>
       <c r="D8">
-        <v>1.44429101603097</v>
+        <v>428944527.4536663</v>
       </c>
       <c r="E8">
-        <v>4.023931040476961</v>
+        <v>33323604.38352972</v>
       </c>
       <c r="F8">
-        <v>1.263133575304094</v>
+        <v>271330480.335582</v>
       </c>
       <c r="G8">
-        <v>0.9135861177445659</v>
+        <v>735372507.5699297</v>
       </c>
       <c r="H8">
-        <v>1.753375622555582</v>
+        <v>201617082.2916511</v>
       </c>
       <c r="I8">
-        <v>3.471056088971512</v>
+        <v>51886377.693913</v>
       </c>
       <c r="J8">
-        <v>3.754212598177478</v>
+        <v>49037063.29213571</v>
       </c>
       <c r="K8">
-        <v>5.305156793080918</v>
+        <v>25103019.39449988</v>
       </c>
       <c r="L8">
-        <v>0.7225256073406711</v>
+        <v>1054708783.406604</v>
       </c>
       <c r="M8">
-        <v>1.085149469580358</v>
+        <v>383310081.2483336</v>
       </c>
     </row>
     <row r="9">
@@ -5240,40 +9269,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.638682473558011</v>
+        <v>324221211.8965963</v>
       </c>
       <c r="C9">
-        <v>5.063181003422212</v>
+        <v>18087568.19715717</v>
       </c>
       <c r="D9">
-        <v>1.226381160701225</v>
+        <v>446074827.4507325</v>
       </c>
       <c r="E9">
-        <v>4.015043996618119</v>
+        <v>34616528.67699277</v>
       </c>
       <c r="F9">
-        <v>1.361185206787635</v>
+        <v>271421234.5764591</v>
       </c>
       <c r="G9">
-        <v>0.8862266980726554</v>
+        <v>744672085.2323104</v>
       </c>
       <c r="H9">
-        <v>1.633889242678157</v>
+        <v>211018998.6827414</v>
       </c>
       <c r="I9">
-        <v>3.406168943776743</v>
+        <v>55921655.13192838</v>
       </c>
       <c r="J9">
-        <v>3.443799826253133</v>
+        <v>49082124.62588678</v>
       </c>
       <c r="K9">
-        <v>4.685332002871649</v>
+        <v>21117979.40518899</v>
       </c>
       <c r="L9">
-        <v>0.6916745269833164</v>
+        <v>1102951094.842443</v>
       </c>
       <c r="M9">
-        <v>1.132221240548153</v>
+        <v>381731907.311692</v>
       </c>
     </row>
     <row r="10">
@@ -5283,40 +9312,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.924560714078346</v>
+        <v>304191339.1482104</v>
       </c>
       <c r="C10">
-        <v>7.986339015503703</v>
+        <v>18845324.12837609</v>
       </c>
       <c r="D10">
-        <v>1.502441303672767</v>
+        <v>408235902.7369107</v>
       </c>
       <c r="E10">
-        <v>4.548931694587989</v>
+        <v>30275628.35355127</v>
       </c>
       <c r="F10">
-        <v>1.527918343828601</v>
+        <v>244213248.3804592</v>
       </c>
       <c r="G10">
-        <v>0.920583112562974</v>
+        <v>683941080.9622746</v>
       </c>
       <c r="H10">
-        <v>2.011702199770191</v>
+        <v>197757168.4187831</v>
       </c>
       <c r="I10">
-        <v>3.98888836219614</v>
+        <v>53179790.47146353</v>
       </c>
       <c r="J10">
-        <v>3.684415938264253</v>
+        <v>47891213.9357496</v>
       </c>
       <c r="K10">
-        <v>5.888869771801783</v>
+        <v>20400470.84383656</v>
       </c>
       <c r="L10">
-        <v>0.8671276060074106</v>
+        <v>956404004.2817293</v>
       </c>
       <c r="M10">
-        <v>1.27562436525766</v>
+        <v>380105891.484383</v>
       </c>
     </row>
     <row r="11">
@@ -5326,40 +9355,40 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.948623552848866</v>
+        <v>338577784.6010824</v>
       </c>
       <c r="C11">
-        <v>6.970428238489861</v>
+        <v>18665362.76173786</v>
       </c>
       <c r="D11">
-        <v>1.672239201632864</v>
+        <v>422506286.9376808</v>
       </c>
       <c r="E11">
-        <v>4.944690233067396</v>
+        <v>26206205.64631877</v>
       </c>
       <c r="F11">
-        <v>1.7422154373825</v>
+        <v>266257467.6783404</v>
       </c>
       <c r="G11">
-        <v>1.081207125435421</v>
+        <v>694764419.2762103</v>
       </c>
       <c r="H11">
-        <v>2.203990314057491</v>
+        <v>194386183.5986514</v>
       </c>
       <c r="I11">
-        <v>3.66346617520867</v>
+        <v>59121925.41857499</v>
       </c>
       <c r="J11">
-        <v>4.899626414403922</v>
+        <v>52107411.02025436</v>
       </c>
       <c r="K11">
-        <v>6.483398151383837</v>
+        <v>24210949.38180474</v>
       </c>
       <c r="L11">
-        <v>0.8918631105909106</v>
+        <v>961518326.0154016</v>
       </c>
       <c r="M11">
-        <v>1.373195938709162</v>
+        <v>380108420.2618977</v>
       </c>
     </row>
     <row r="12">
@@ -5369,40 +9398,40 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.92619603271823</v>
+        <v>323944534.6488771</v>
       </c>
       <c r="C12">
-        <v>6.025587035886979</v>
+        <v>20937512.44074901</v>
       </c>
       <c r="D12">
-        <v>1.415326353718094</v>
+        <v>446340549.4638312</v>
       </c>
       <c r="E12">
-        <v>4.458790941810822</v>
+        <v>28905792.52165256</v>
       </c>
       <c r="F12">
-        <v>1.50300894969205</v>
+        <v>284814462.8227397</v>
       </c>
       <c r="G12">
-        <v>0.9285480188636875</v>
+        <v>762379099.3524714</v>
       </c>
       <c r="H12">
-        <v>1.852531593458228</v>
+        <v>220105472.6905506</v>
       </c>
       <c r="I12">
-        <v>3.477010562101077</v>
+        <v>68512808.21877678</v>
       </c>
       <c r="J12">
-        <v>3.985825969827106</v>
+        <v>58246545.4182791</v>
       </c>
       <c r="K12">
-        <v>5.485150124811742</v>
+        <v>23897306.97495419</v>
       </c>
       <c r="L12">
-        <v>0.7329861141513896</v>
+        <v>1091111605.746589</v>
       </c>
       <c r="M12">
-        <v>1.138217257955315</v>
+        <v>401359577.5944006</v>
       </c>
     </row>
     <row r="13">
@@ -5412,40 +9441,40 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.819936790958393</v>
+        <v>311223545.8536829</v>
       </c>
       <c r="C13">
-        <v>6.991798980622777</v>
+        <v>22489875.2899164</v>
       </c>
       <c r="D13">
-        <v>1.495690834930072</v>
+        <v>464002520.2962453</v>
       </c>
       <c r="E13">
-        <v>4.891730512840009</v>
+        <v>29415983.46938587</v>
       </c>
       <c r="F13">
-        <v>1.560637326786331</v>
+        <v>289292256.6490241</v>
       </c>
       <c r="G13">
-        <v>0.9414849592320836</v>
+        <v>782463699.8204015</v>
       </c>
       <c r="H13">
-        <v>1.761887882809969</v>
+        <v>230708416.5520212</v>
       </c>
       <c r="I13">
-        <v>3.253118401568827</v>
+        <v>72641274.35856512</v>
       </c>
       <c r="J13">
-        <v>3.626275208150731</v>
+        <v>60502199.10129788</v>
       </c>
       <c r="K13">
-        <v>4.837148174263797</v>
+        <v>26990231.4132628</v>
       </c>
       <c r="L13">
-        <v>0.6972026071527506</v>
+        <v>1168329041.030335</v>
       </c>
       <c r="M13">
-        <v>1.250741035052319</v>
+        <v>415574317.208721</v>
       </c>
     </row>
     <row r="14">
@@ -5455,40 +9484,40 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.671353322476085</v>
+        <v>300551136.9657424</v>
       </c>
       <c r="C14">
-        <v>5.682299260829111</v>
+        <v>23238749.17807949</v>
       </c>
       <c r="D14">
-        <v>1.520874858780017</v>
+        <v>477443770.820662</v>
       </c>
       <c r="E14">
-        <v>3.945699332256952</v>
+        <v>30881397.53501778</v>
       </c>
       <c r="F14">
-        <v>1.179360264513972</v>
+        <v>306288875.499263</v>
       </c>
       <c r="G14">
-        <v>0.9247358516158158</v>
+        <v>812054691.4099022</v>
       </c>
       <c r="H14">
-        <v>1.558962472815284</v>
+        <v>249993862.0444941</v>
       </c>
       <c r="I14">
-        <v>2.865592505559784</v>
+        <v>69232425.22691368</v>
       </c>
       <c r="J14">
-        <v>3.707098843407498</v>
+        <v>61051960.84754699</v>
       </c>
       <c r="K14">
-        <v>5.200210501392466</v>
+        <v>29308512.66538075</v>
       </c>
       <c r="L14">
-        <v>0.6766218143124243</v>
+        <v>1190942352.871505</v>
       </c>
       <c r="M14">
-        <v>1.093303390373478</v>
+        <v>431447551.6723856</v>
       </c>
     </row>
     <row r="15">
@@ -5498,40 +9527,40 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.8999678015670664</v>
+        <v>888577491.3695906</v>
       </c>
       <c r="C15">
-        <v>2.813963177507366</v>
+        <v>75598483.63268439</v>
       </c>
       <c r="D15">
-        <v>0.6395298716481574</v>
+        <v>1452293684.269937</v>
       </c>
       <c r="E15">
-        <v>2.228962182796911</v>
+        <v>93449674.91292156</v>
       </c>
       <c r="F15">
-        <v>0.799710715001933</v>
+        <v>878179463.7520581</v>
       </c>
       <c r="G15">
-        <v>0.4592090784211751</v>
+        <v>2417420399.35941</v>
       </c>
       <c r="H15">
-        <v>0.9249966893057747</v>
+        <v>759980420.0934938</v>
       </c>
       <c r="I15">
-        <v>1.43913912459358</v>
+        <v>215313931.9243874</v>
       </c>
       <c r="J15">
-        <v>1.723133202358719</v>
+        <v>193441665.1132816</v>
       </c>
       <c r="K15">
-        <v>2.609372426026087</v>
+        <v>90417580.36192513</v>
       </c>
       <c r="L15">
-        <v>0.3810541173167093</v>
+        <v>3582523698.425214</v>
       </c>
       <c r="M15">
-        <v>0.5570082515932762</v>
+        <v>1313414138.88015</v>
       </c>
     </row>
   </sheetData>
@@ -5618,40 +9647,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.305006849996661</v>
+        <v>369025811.3532501</v>
       </c>
       <c r="C2">
-        <v>5.653509282231969</v>
+        <v>22133442.73217437</v>
       </c>
       <c r="D2">
-        <v>1.197306302273826</v>
+        <v>464531820.4942085</v>
       </c>
       <c r="E2">
-        <v>3.668857617627128</v>
+        <v>31212265.69152835</v>
       </c>
       <c r="F2">
-        <v>1.195180785135504</v>
+        <v>298720623.2920421</v>
       </c>
       <c r="G2">
-        <v>0.8779734722253659</v>
+        <v>720694175.7974776</v>
       </c>
       <c r="H2">
-        <v>1.680349563209922</v>
+        <v>188234457.1517739</v>
       </c>
       <c r="I2">
-        <v>3.77462609993864</v>
+        <v>48659144.77859067</v>
       </c>
       <c r="J2">
-        <v>3.667363136725615</v>
+        <v>45231041.20392935</v>
       </c>
       <c r="K2">
-        <v>4.988691871370069</v>
+        <v>21391181.9684962</v>
       </c>
       <c r="L2">
-        <v>0.6709603721965898</v>
+        <v>900192078.0692487</v>
       </c>
       <c r="M2">
-        <v>1.1321813115778</v>
+        <v>336704394.188238</v>
       </c>
     </row>
     <row r="3">
@@ -5661,40 +9690,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.252336183638528</v>
+        <v>364350595.8079318</v>
       </c>
       <c r="C3">
-        <v>5.751911789310947</v>
+        <v>22937113.59885124</v>
       </c>
       <c r="D3">
-        <v>1.213421141156759</v>
+        <v>454366191.8247328</v>
       </c>
       <c r="E3">
-        <v>3.349157098690275</v>
+        <v>35257804.27675927</v>
       </c>
       <c r="F3">
-        <v>1.169532700932448</v>
+        <v>320020228.1299685</v>
       </c>
       <c r="G3">
-        <v>0.8038374123209355</v>
+        <v>731794623.8557931</v>
       </c>
       <c r="H3">
-        <v>1.776766519567841</v>
+        <v>183239886.3358048</v>
       </c>
       <c r="I3">
-        <v>3.669895651884866</v>
+        <v>51922272.68950664</v>
       </c>
       <c r="J3">
-        <v>3.166909075496505</v>
+        <v>48569524.60515544</v>
       </c>
       <c r="K3">
-        <v>4.740781709559833</v>
+        <v>21525406.12665416</v>
       </c>
       <c r="L3">
-        <v>0.6528519925100977</v>
+        <v>936139323.1783297</v>
       </c>
       <c r="M3">
-        <v>1.204533533498913</v>
+        <v>340085313.1913055</v>
       </c>
     </row>
     <row r="4">
@@ -5704,40 +9733,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.359220133713039</v>
+        <v>340408261.0939456</v>
       </c>
       <c r="C4">
-        <v>4.701650814860233</v>
+        <v>20408532.34565331</v>
       </c>
       <c r="D4">
-        <v>1.299202243567142</v>
+        <v>478518744.1168303</v>
       </c>
       <c r="E4">
-        <v>3.553395210229854</v>
+        <v>36615717.81393786</v>
       </c>
       <c r="F4">
-        <v>1.391669211929121</v>
+        <v>311611999.3399818</v>
       </c>
       <c r="G4">
-        <v>0.8307040801180384</v>
+        <v>729106494.7246021</v>
       </c>
       <c r="H4">
-        <v>1.737588338881049</v>
+        <v>188547525.7586206</v>
       </c>
       <c r="I4">
-        <v>3.455649569770459</v>
+        <v>51416943.44661222</v>
       </c>
       <c r="J4">
-        <v>3.652792425811044</v>
+        <v>49147416.71561068</v>
       </c>
       <c r="K4">
-        <v>5.848595054747506</v>
+        <v>23181159.64110783</v>
       </c>
       <c r="L4">
-        <v>0.7100814491485826</v>
+        <v>954893987.8326925</v>
       </c>
       <c r="M4">
-        <v>1.184179007361313</v>
+        <v>346262947.7244508</v>
       </c>
     </row>
     <row r="5">
@@ -5747,40 +9776,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.334018642497567</v>
+        <v>328884361.9180166</v>
       </c>
       <c r="C5">
-        <v>6.014963535817675</v>
+        <v>20569850.60365238</v>
       </c>
       <c r="D5">
-        <v>1.338943033058063</v>
+        <v>451227831.2896565</v>
       </c>
       <c r="E5">
-        <v>3.729428555311892</v>
+        <v>34788792.33221267</v>
       </c>
       <c r="F5">
-        <v>1.501638496183817</v>
+        <v>298964337.3206134</v>
       </c>
       <c r="G5">
-        <v>0.8672584823301503</v>
+        <v>727016683.5456718</v>
       </c>
       <c r="H5">
-        <v>1.750687528927887</v>
+        <v>185026317.4262761</v>
       </c>
       <c r="I5">
-        <v>3.271940604366938</v>
+        <v>47834561.14016985</v>
       </c>
       <c r="J5">
-        <v>3.309311273903474</v>
+        <v>46153862.2475606</v>
       </c>
       <c r="K5">
-        <v>5.12576589342913</v>
+        <v>24179885.17530768</v>
       </c>
       <c r="L5">
-        <v>0.7119088707655105</v>
+        <v>973597464.6762034</v>
       </c>
       <c r="M5">
-        <v>1.101132549397676</v>
+        <v>347124166.2286649</v>
       </c>
     </row>
     <row r="6">
@@ -5790,40 +9819,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.489606244591462</v>
+        <v>325135746.55463</v>
       </c>
       <c r="C6">
-        <v>5.849797506145743</v>
+        <v>18363779.77654604</v>
       </c>
       <c r="D6">
-        <v>1.459216757079727</v>
+        <v>405399052.1105905</v>
       </c>
       <c r="E6">
-        <v>5.464630470909245</v>
+        <v>29261381.2371389</v>
       </c>
       <c r="F6">
-        <v>1.456831829497377</v>
+        <v>288769401.619698</v>
       </c>
       <c r="G6">
-        <v>0.8947745756012778</v>
+        <v>709259869.8288544</v>
       </c>
       <c r="H6">
-        <v>1.903347860279486</v>
+        <v>190700483.8204682</v>
       </c>
       <c r="I6">
-        <v>3.58737392613075</v>
+        <v>49884717.7303407</v>
       </c>
       <c r="J6">
-        <v>4.329577150910105</v>
+        <v>46278009.02173458</v>
       </c>
       <c r="K6">
-        <v>4.914921930090728</v>
+        <v>20708450.89111576</v>
       </c>
       <c r="L6">
-        <v>0.7931071223471037</v>
+        <v>980353412.0541972</v>
       </c>
       <c r="M6">
-        <v>1.210889539770282</v>
+        <v>349899244.8324967</v>
       </c>
     </row>
     <row r="7">
@@ -5833,40 +9862,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.697520734876659</v>
+        <v>312460145.0532829</v>
       </c>
       <c r="C7">
-        <v>5.458507069989448</v>
+        <v>15855565.67206406</v>
       </c>
       <c r="D7">
-        <v>1.375129756485082</v>
+        <v>408746478.2658709</v>
       </c>
       <c r="E7">
-        <v>3.958865698264977</v>
+        <v>32897532.59303574</v>
       </c>
       <c r="F7">
-        <v>1.434339795381329</v>
+        <v>267642864.2834446</v>
       </c>
       <c r="G7">
-        <v>0.8759051760533968</v>
+        <v>701083189.3172793</v>
       </c>
       <c r="H7">
-        <v>1.677933055425201</v>
+        <v>186556948.4685434</v>
       </c>
       <c r="I7">
-        <v>3.862503674449367</v>
+        <v>47450838.10908892</v>
       </c>
       <c r="J7">
-        <v>3.89332510240765</v>
+        <v>44767566.05550248</v>
       </c>
       <c r="K7">
-        <v>4.63663707271178</v>
+        <v>21636011.6368094</v>
       </c>
       <c r="L7">
-        <v>0.7418336533483704</v>
+        <v>983252524.3339462</v>
       </c>
       <c r="M7">
-        <v>1.108480960519967</v>
+        <v>347415776.4569154</v>
       </c>
     </row>
     <row r="8">
@@ -5876,40 +9905,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.416334095676617</v>
+        <v>308558131.9674813</v>
       </c>
       <c r="C8">
-        <v>6.194745140479269</v>
+        <v>18474072.72529914</v>
       </c>
       <c r="D8">
-        <v>1.474172993220126</v>
+        <v>406856104.1065894</v>
       </c>
       <c r="E8">
-        <v>4.135480850268473</v>
+        <v>32324079.35171078</v>
       </c>
       <c r="F8">
-        <v>1.26601978758067</v>
+        <v>255816763.6565019</v>
       </c>
       <c r="G8">
-        <v>0.9061201686906668</v>
+        <v>706945997.7596751</v>
       </c>
       <c r="H8">
-        <v>1.75251055601295</v>
+        <v>192069868.4995778</v>
       </c>
       <c r="I8">
-        <v>3.678170242991729</v>
+        <v>49411108.07117373</v>
       </c>
       <c r="J8">
-        <v>3.960382050391352</v>
+        <v>46810189.76419434</v>
       </c>
       <c r="K8">
-        <v>5.437967976303223</v>
+        <v>24217621.35175027</v>
       </c>
       <c r="L8">
-        <v>0.7375812932884701</v>
+        <v>1013413376.404422</v>
       </c>
       <c r="M8">
-        <v>1.125860881609441</v>
+        <v>357496429.7661119</v>
       </c>
     </row>
     <row r="9">
@@ -5919,40 +9948,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.650781155415802</v>
+        <v>312288436.3248178</v>
       </c>
       <c r="C9">
-        <v>5.222846107665599</v>
+        <v>17148004.45670659</v>
       </c>
       <c r="D9">
-        <v>1.243387540237515</v>
+        <v>427522284.515403</v>
       </c>
       <c r="E9">
-        <v>4.067391890332972</v>
+        <v>32816319.73984313</v>
       </c>
       <c r="F9">
-        <v>1.394134984763305</v>
+        <v>258063101.2255936</v>
       </c>
       <c r="G9">
-        <v>0.9028503890142432</v>
+        <v>723027684.1507826</v>
       </c>
       <c r="H9">
-        <v>1.595319412359596</v>
+        <v>201150762.4380421</v>
       </c>
       <c r="I9">
-        <v>3.458541747201571</v>
+        <v>53663661.2608085</v>
       </c>
       <c r="J9">
-        <v>3.483328337998869</v>
+        <v>47485842.59504908</v>
       </c>
       <c r="K9">
-        <v>4.813569882290358</v>
+        <v>20383501.04602155</v>
       </c>
       <c r="L9">
-        <v>0.7096697947960776</v>
+        <v>1062130766.345432</v>
       </c>
       <c r="M9">
-        <v>1.156126342008376</v>
+        <v>355562448.7618134</v>
       </c>
     </row>
     <row r="10">
@@ -5962,40 +9991,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.958861904980206</v>
+        <v>288358579.9463026</v>
       </c>
       <c r="C10">
-        <v>8.225974922357942</v>
+        <v>16894465.37097295</v>
       </c>
       <c r="D10">
-        <v>1.588804929060806</v>
+        <v>361827327.805424</v>
       </c>
       <c r="E10">
-        <v>4.874041378254197</v>
+        <v>26722883.41745002</v>
       </c>
       <c r="F10">
-        <v>1.63577847431798</v>
+        <v>214036578.5700764</v>
       </c>
       <c r="G10">
-        <v>1.015428947928249</v>
+        <v>618739335.3411539</v>
       </c>
       <c r="H10">
-        <v>2.195847213171828</v>
+        <v>172035734.5178932</v>
       </c>
       <c r="I10">
-        <v>3.940951158673476</v>
+        <v>48203064.97932896</v>
       </c>
       <c r="J10">
-        <v>3.828767196988058</v>
+        <v>43974998.99690106</v>
       </c>
       <c r="K10">
-        <v>6.213818437765056</v>
+        <v>17713917.24397814</v>
       </c>
       <c r="L10">
-        <v>0.9626500996606613</v>
+        <v>821443506.1682211</v>
       </c>
       <c r="M10">
-        <v>1.430416185621493</v>
+        <v>319263609.0425953</v>
       </c>
     </row>
     <row r="11">
@@ -6005,40 +10034,40 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.979815178819489</v>
+        <v>327951747.0783319</v>
       </c>
       <c r="C11">
-        <v>6.741508442756938</v>
+        <v>17881273.49511092</v>
       </c>
       <c r="D11">
-        <v>1.707128510353901</v>
+        <v>405061474.0449448</v>
       </c>
       <c r="E11">
-        <v>5.064559890619647</v>
+        <v>25456297.65010785</v>
       </c>
       <c r="F11">
-        <v>1.756455596764365</v>
+        <v>252459532.4784293</v>
       </c>
       <c r="G11">
-        <v>1.095781990591572</v>
+        <v>670035578.7174108</v>
       </c>
       <c r="H11">
-        <v>2.334638082983152</v>
+        <v>186350682.2634681</v>
       </c>
       <c r="I11">
-        <v>3.753475437329971</v>
+        <v>57730285.32185305</v>
       </c>
       <c r="J11">
-        <v>4.955764141795985</v>
+        <v>50315491.20843335</v>
       </c>
       <c r="K11">
-        <v>6.592301832569827</v>
+        <v>22993400.61629088</v>
       </c>
       <c r="L11">
-        <v>0.8596684569857418</v>
+        <v>918360058.5080187</v>
       </c>
       <c r="M11">
-        <v>1.395402036870331</v>
+        <v>357793153.8322756</v>
       </c>
     </row>
     <row r="12">
@@ -6048,40 +10077,40 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.944617853469676</v>
+        <v>312255361.3802723</v>
       </c>
       <c r="C12">
-        <v>6.198951502591198</v>
+        <v>19643153.43058299</v>
       </c>
       <c r="D12">
-        <v>1.46473977806212</v>
+        <v>427166428.6689038</v>
       </c>
       <c r="E12">
-        <v>4.575262527110037</v>
+        <v>28078156.81122961</v>
       </c>
       <c r="F12">
-        <v>1.504449199380579</v>
+        <v>271614761.77892</v>
       </c>
       <c r="G12">
-        <v>0.9260184815406469</v>
+        <v>741301636.1368331</v>
       </c>
       <c r="H12">
-        <v>1.894998465357184</v>
+        <v>212905152.5638032</v>
       </c>
       <c r="I12">
-        <v>3.564682682401704</v>
+        <v>66260894.86445766</v>
       </c>
       <c r="J12">
-        <v>4.05355390012316</v>
+        <v>55279565.92908355</v>
       </c>
       <c r="K12">
-        <v>5.56996429634277</v>
+        <v>23287653.31718835</v>
       </c>
       <c r="L12">
-        <v>0.7607771082353829</v>
+        <v>1057512620.516456</v>
       </c>
       <c r="M12">
-        <v>1.18307550824296</v>
+        <v>379681563.069118</v>
       </c>
     </row>
     <row r="13">
@@ -6091,40 +10120,40 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.841289926008275</v>
+        <v>300658232.1300274</v>
       </c>
       <c r="C13">
-        <v>7.201051051998762</v>
+        <v>22070280.86796557</v>
       </c>
       <c r="D13">
-        <v>1.531515610847452</v>
+        <v>448037403.8663678</v>
       </c>
       <c r="E13">
-        <v>4.821086774887509</v>
+        <v>28109455.68077762</v>
       </c>
       <c r="F13">
-        <v>1.585435925636496</v>
+        <v>277933983.6535088</v>
       </c>
       <c r="G13">
-        <v>0.9561656319515622</v>
+        <v>762154898.1871977</v>
       </c>
       <c r="H13">
-        <v>1.772368231121621</v>
+        <v>222846498.7252631</v>
       </c>
       <c r="I13">
-        <v>3.364440577859422</v>
+        <v>71294790.28050022</v>
       </c>
       <c r="J13">
-        <v>3.739794667225761</v>
+        <v>58324687.31834503</v>
       </c>
       <c r="K13">
-        <v>4.951547273627031</v>
+        <v>25834132.53724833</v>
       </c>
       <c r="L13">
-        <v>0.7132663716317986</v>
+        <v>1131058686.189108</v>
       </c>
       <c r="M13">
-        <v>1.27332107883046</v>
+        <v>391681727.7588437</v>
       </c>
     </row>
     <row r="14">
@@ -6134,40 +10163,40 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.702795472518328</v>
+        <v>289766525.7158094</v>
       </c>
       <c r="C14">
-        <v>5.831695903393473</v>
+        <v>22406007.41440223</v>
       </c>
       <c r="D14">
-        <v>1.504882961300219</v>
+        <v>462126765.4076072</v>
       </c>
       <c r="E14">
-        <v>4.026146835121498</v>
+        <v>30274456.55524277</v>
       </c>
       <c r="F14">
-        <v>1.181128338283655</v>
+        <v>293285591.2777665</v>
       </c>
       <c r="G14">
-        <v>0.9316906324653299</v>
+        <v>792039355.9497182</v>
       </c>
       <c r="H14">
-        <v>1.583277728037602</v>
+        <v>240374370.2955453</v>
       </c>
       <c r="I14">
-        <v>2.950793993238633</v>
+        <v>67549322.00954562</v>
       </c>
       <c r="J14">
-        <v>3.664690107327911</v>
+        <v>58710563.88455723</v>
       </c>
       <c r="K14">
-        <v>5.310771575203762</v>
+        <v>28453161.94852677</v>
       </c>
       <c r="L14">
-        <v>0.6975239629786576</v>
+        <v>1153249923.683223</v>
       </c>
       <c r="M14">
-        <v>1.144246451021685</v>
+        <v>408525277.7641805</v>
       </c>
     </row>
     <row r="15">
@@ -6177,40 +10206,40 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.9045656342424747</v>
+        <v>856197217.6228412</v>
       </c>
       <c r="C15">
-        <v>2.859925527163085</v>
+        <v>72428965.24884325</v>
       </c>
       <c r="D15">
-        <v>0.6379692883914083</v>
+        <v>1401126885.264667</v>
       </c>
       <c r="E15">
-        <v>2.249393408384412</v>
+        <v>90597747.45910963</v>
       </c>
       <c r="F15">
-        <v>0.802945293988511</v>
+        <v>843995517.7034504</v>
       </c>
       <c r="G15">
-        <v>0.473413702937625</v>
+        <v>2350169419.480287</v>
       </c>
       <c r="H15">
-        <v>0.9254915182038161</v>
+        <v>735893185.3919363</v>
       </c>
       <c r="I15">
-        <v>1.456814067186478</v>
+        <v>211111940.9411427</v>
       </c>
       <c r="J15">
-        <v>1.803231322638735</v>
+        <v>186094996.7298087</v>
       </c>
       <c r="K15">
-        <v>2.632876030072033</v>
+        <v>87958434.77823001</v>
       </c>
       <c r="L15">
-        <v>0.3864781788635187</v>
+        <v>3466905155.027363</v>
       </c>
       <c r="M15">
-        <v>0.5631242030042563</v>
+        <v>1241008888.009439</v>
       </c>
     </row>
   </sheetData>
@@ -6297,40 +10326,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>4.059863130783381</v>
+        <v>44865.81416728</v>
       </c>
       <c r="C2">
-        <v>36.18573255192801</v>
+        <v>595.63299924</v>
       </c>
       <c r="D2">
-        <v>7.237901258935024</v>
+        <v>13579.19759981</v>
       </c>
       <c r="E2">
-        <v>26.02544530087286</v>
+        <v>1134.14754132</v>
       </c>
       <c r="F2">
-        <v>8.115475344088313</v>
+        <v>8019.2560165</v>
       </c>
       <c r="G2">
-        <v>4.631057247068334</v>
+        <v>23756.15348941</v>
       </c>
       <c r="H2">
-        <v>9.724253141976986</v>
+        <v>8958.305337829999</v>
       </c>
       <c r="I2">
-        <v>14.19546106079139</v>
+        <v>3893.22335437</v>
       </c>
       <c r="J2">
-        <v>20.1384398073133</v>
+        <v>895.48157324</v>
       </c>
       <c r="K2">
-        <v>21.86440260705363</v>
+        <v>1233.5267968</v>
       </c>
       <c r="L2">
-        <v>3.24460575231796</v>
+        <v>84484.24312078999</v>
       </c>
       <c r="M2">
-        <v>3.960427438933731</v>
+        <v>45403.38566431</v>
       </c>
     </row>
     <row r="3">
@@ -6340,40 +10369,37 @@
         </is>
       </c>
       <c r="B3">
-        <v>4.456184711391191</v>
+        <v>47085.99901669</v>
       </c>
       <c r="C3">
-        <v>49.90586574359943</v>
+        <v>583.84461237</v>
       </c>
       <c r="D3">
-        <v>7.864138948003234</v>
-      </c>
-      <c r="E3">
-        <v>29.58538137703795</v>
+        <v>15853.54919619</v>
       </c>
       <c r="F3">
-        <v>8.362225731481535</v>
+        <v>8741.055800169999</v>
       </c>
       <c r="G3">
-        <v>4.4388177720854</v>
+        <v>24549.14415362</v>
       </c>
       <c r="H3">
-        <v>9.212961203342557</v>
+        <v>8150.41873738</v>
       </c>
       <c r="I3">
-        <v>15.35971374221546</v>
+        <v>4850.91031507</v>
       </c>
       <c r="J3">
-        <v>24.3021019727747</v>
+        <v>3084.6519967</v>
       </c>
       <c r="K3">
-        <v>22.53193752272647</v>
+        <v>2647.89402193</v>
       </c>
       <c r="L3">
-        <v>3.108374359499403</v>
+        <v>114838.94415582</v>
       </c>
       <c r="M3">
-        <v>3.562312652292583</v>
+        <v>50195.41199763</v>
       </c>
     </row>
     <row r="4">
@@ -6383,40 +10409,37 @@
         </is>
       </c>
       <c r="B4">
-        <v>4.512773463553723</v>
+        <v>43900.11952049</v>
       </c>
       <c r="C4">
-        <v>51.6836409473604</v>
+        <v>622.69557659</v>
       </c>
       <c r="D4">
-        <v>8.05777664229052</v>
-      </c>
-      <c r="E4">
-        <v>39.28249324753122</v>
+        <v>12931.54466897</v>
       </c>
       <c r="F4">
-        <v>8.919022069548209</v>
+        <v>11557.25625633</v>
       </c>
       <c r="G4">
-        <v>4.653303124749239</v>
+        <v>32328.41397373</v>
       </c>
       <c r="H4">
-        <v>11.02072783578842</v>
+        <v>8062.85538541</v>
       </c>
       <c r="I4">
-        <v>21.35839166799103</v>
+        <v>3337.73435612</v>
       </c>
       <c r="J4">
-        <v>31.24505805462546</v>
+        <v>777.6001092299999</v>
       </c>
       <c r="K4">
-        <v>28.13176855112123</v>
+        <v>1760.54460141</v>
       </c>
       <c r="L4">
-        <v>3.468991326474549</v>
+        <v>115766.54030916</v>
       </c>
       <c r="M4">
-        <v>3.301116636262151</v>
+        <v>51057.08810576</v>
       </c>
     </row>
     <row r="5">
@@ -6426,40 +10449,34 @@
         </is>
       </c>
       <c r="B5">
-        <v>4.254624257834429</v>
-      </c>
-      <c r="C5">
-        <v>50.99827002543527</v>
+        <v>50213.46599731</v>
       </c>
       <c r="D5">
-        <v>14.89962484436577</v>
-      </c>
-      <c r="E5">
-        <v>27.73063615717873</v>
+        <v>19531.02396868</v>
       </c>
       <c r="F5">
-        <v>9.369940591565383</v>
+        <v>7517.27559017</v>
       </c>
       <c r="G5">
-        <v>5.029769781447802</v>
+        <v>30470.26083798</v>
       </c>
       <c r="H5">
-        <v>10.47002682371572</v>
+        <v>7090.32299693</v>
       </c>
       <c r="I5">
-        <v>18.40489847064787</v>
+        <v>1857.06909712</v>
       </c>
       <c r="J5">
-        <v>38.11389323874109</v>
+        <v>730.4565896500001</v>
       </c>
       <c r="K5">
-        <v>24.53436227803618</v>
+        <v>853.7624083599999</v>
       </c>
       <c r="L5">
-        <v>3.033759720794181</v>
+        <v>105959.6990462</v>
       </c>
       <c r="M5">
-        <v>3.560869987474548</v>
+        <v>59230.08493636</v>
       </c>
     </row>
     <row r="6">
@@ -6469,40 +10486,37 @@
         </is>
       </c>
       <c r="B6">
-        <v>5.408548951371876</v>
-      </c>
-      <c r="C6">
-        <v>78.36934406985701</v>
+        <v>42002.43934282</v>
       </c>
       <c r="D6">
-        <v>9.400001009141814</v>
+        <v>12057.23569009</v>
       </c>
       <c r="E6">
-        <v>41.5105754978265</v>
+        <v>908.54267712</v>
       </c>
       <c r="F6">
-        <v>10.3850169308272</v>
+        <v>3212.48150231</v>
       </c>
       <c r="G6">
-        <v>4.887257911731209</v>
+        <v>17954.10682484</v>
       </c>
       <c r="H6">
-        <v>10.44575790572381</v>
+        <v>8860.459100460001</v>
       </c>
       <c r="I6">
-        <v>17.06256002737261</v>
+        <v>1615.37886527</v>
       </c>
       <c r="J6">
-        <v>36.71626928241853</v>
+        <v>422.33827618</v>
       </c>
       <c r="K6">
-        <v>34.23990412062709</v>
+        <v>471.79285451</v>
       </c>
       <c r="L6">
-        <v>3.584475445105197</v>
+        <v>90531.27076956999</v>
       </c>
       <c r="M6">
-        <v>4.601226769810667</v>
+        <v>39546.41486495</v>
       </c>
     </row>
     <row r="7">
@@ -6512,40 +10526,34 @@
         </is>
       </c>
       <c r="B7">
-        <v>5.086359868514235</v>
-      </c>
-      <c r="C7">
-        <v>104.2846320532687</v>
+        <v>67354.43543668999</v>
       </c>
       <c r="D7">
-        <v>7.892610588697628</v>
-      </c>
-      <c r="E7">
-        <v>39.77392162725822</v>
+        <v>9240.136695380001</v>
       </c>
       <c r="F7">
-        <v>10.87638387986763</v>
+        <v>7813.92989587</v>
       </c>
       <c r="G7">
-        <v>5.392830102018797</v>
+        <v>25928.16954223</v>
       </c>
       <c r="H7">
-        <v>8.508285734706956</v>
+        <v>10687.00785953</v>
       </c>
       <c r="I7">
-        <v>14.71214369498658</v>
+        <v>1913.36242016</v>
       </c>
       <c r="J7">
-        <v>22.98911703839407</v>
+        <v>1074.17706304</v>
       </c>
       <c r="K7">
-        <v>20.43756021294822</v>
+        <v>1907.04065761</v>
       </c>
       <c r="L7">
-        <v>3.410317674826491</v>
+        <v>113186.75624591</v>
       </c>
       <c r="M7">
-        <v>4.058052412962532</v>
+        <v>38055.25302908</v>
       </c>
     </row>
     <row r="8">
@@ -6555,40 +10563,37 @@
         </is>
       </c>
       <c r="B8">
-        <v>4.575913610576653</v>
-      </c>
-      <c r="C8">
-        <v>47.37561941529971</v>
+        <v>55819.55830469</v>
       </c>
       <c r="D8">
-        <v>7.321743436613263</v>
+        <v>14135.68216444</v>
       </c>
       <c r="E8">
-        <v>28.19009401244594</v>
+        <v>581.63372192</v>
       </c>
       <c r="F8">
-        <v>9.203168363060067</v>
+        <v>11423.37428391</v>
       </c>
       <c r="G8">
-        <v>4.882802295292732</v>
+        <v>37258.53349684</v>
       </c>
       <c r="H8">
-        <v>8.663948293389556</v>
+        <v>9402.1810618</v>
       </c>
       <c r="I8">
-        <v>14.92824840553305</v>
+        <v>3406.8466178</v>
       </c>
       <c r="J8">
-        <v>34.39892381811901</v>
+        <v>1220.9703995</v>
       </c>
       <c r="K8">
-        <v>22.78488900498766</v>
+        <v>991.18349201</v>
       </c>
       <c r="L8">
-        <v>2.881145084677367</v>
+        <v>106332.51698632</v>
       </c>
       <c r="M8">
-        <v>4.221146737486448</v>
+        <v>37691.63369072</v>
       </c>
     </row>
     <row r="9">
@@ -6598,40 +10603,37 @@
         </is>
       </c>
       <c r="B9">
-        <v>4.950960688373843</v>
+        <v>55225.44167546</v>
       </c>
       <c r="C9">
-        <v>48.07996233217762</v>
+        <v>170.90309305</v>
       </c>
       <c r="D9">
-        <v>9.369293494457013</v>
-      </c>
-      <c r="E9">
-        <v>51.88599621121307</v>
+        <v>11524.06924892</v>
       </c>
       <c r="F9">
-        <v>10.27712430448128</v>
+        <v>5720.37337192</v>
       </c>
       <c r="G9">
-        <v>5.301691906003475</v>
+        <v>28162.5621921</v>
       </c>
       <c r="H9">
-        <v>8.919877978490314</v>
+        <v>8441.22835653</v>
       </c>
       <c r="I9">
-        <v>17.94996001699316</v>
+        <v>1696.48057743</v>
       </c>
       <c r="J9">
-        <v>23.88874008805884</v>
+        <v>1997.87347135</v>
       </c>
       <c r="K9">
-        <v>27.32684516653704</v>
+        <v>1178.10390405</v>
       </c>
       <c r="L9">
-        <v>2.855391272269095</v>
+        <v>121599.26146982</v>
       </c>
       <c r="M9">
-        <v>3.717564929718125</v>
+        <v>37603.56136762</v>
       </c>
     </row>
     <row r="10">
@@ -6641,40 +10643,34 @@
         </is>
       </c>
       <c r="B10">
-        <v>6.146995829409994</v>
-      </c>
-      <c r="C10">
-        <v>64.52361983893165</v>
+        <v>44576.29356951</v>
       </c>
       <c r="D10">
-        <v>9.913677822534936</v>
-      </c>
-      <c r="E10">
-        <v>81.68128789155851</v>
+        <v>7168.47525402</v>
       </c>
       <c r="F10">
-        <v>17.47966175507566</v>
+        <v>2238.68001786</v>
       </c>
       <c r="G10">
-        <v>7.912987719511523</v>
+        <v>14716.43030282</v>
       </c>
       <c r="H10">
-        <v>13.61053708206212</v>
+        <v>2070.79607497</v>
       </c>
       <c r="I10">
-        <v>20.01479256264921</v>
+        <v>3018.1151686</v>
       </c>
       <c r="J10">
-        <v>29.45627218982454</v>
+        <v>597.10621158</v>
       </c>
       <c r="K10">
-        <v>27.34608018029163</v>
+        <v>750.71611505</v>
       </c>
       <c r="L10">
-        <v>3.87389238256569</v>
+        <v>78018.59805304999</v>
       </c>
       <c r="M10">
-        <v>4.650123639125614</v>
+        <v>32739.22808547</v>
       </c>
     </row>
     <row r="11">
@@ -6684,40 +10680,37 @@
         </is>
       </c>
       <c r="B11">
-        <v>7.123709865915543</v>
+        <v>27165.43809992</v>
       </c>
       <c r="C11">
-        <v>49.52071625682209</v>
+        <v>457.67065491</v>
       </c>
       <c r="D11">
-        <v>11.63204025256062</v>
-      </c>
-      <c r="E11">
-        <v>61.64573826271558</v>
+        <v>8260.908885749999</v>
       </c>
       <c r="F11">
-        <v>13.72352668543922</v>
+        <v>5286.61108609</v>
       </c>
       <c r="G11">
-        <v>7.054900636484198</v>
+        <v>21043.73798484</v>
       </c>
       <c r="H11">
-        <v>10.83334523077282</v>
+        <v>5290.44164979</v>
       </c>
       <c r="I11">
-        <v>22.30445331147673</v>
+        <v>3542.47787025</v>
       </c>
       <c r="J11">
-        <v>29.8691093967415</v>
+        <v>335.58599604</v>
       </c>
       <c r="K11">
-        <v>28.91691029973866</v>
+        <v>1499.39015131</v>
       </c>
       <c r="L11">
-        <v>4.889166824120265</v>
+        <v>67712.92236000999</v>
       </c>
       <c r="M11">
-        <v>4.965948470093847</v>
+        <v>29124.1332089</v>
       </c>
     </row>
     <row r="12">
@@ -6727,40 +10720,37 @@
         </is>
       </c>
       <c r="B12">
-        <v>7.250413383394466</v>
+        <v>39059.67151178</v>
       </c>
       <c r="C12">
-        <v>60.56846149745289</v>
+        <v>174.73897293</v>
       </c>
       <c r="D12">
-        <v>10.7910118192191</v>
-      </c>
-      <c r="E12">
-        <v>44.18003841220329</v>
+        <v>8724.40828023</v>
       </c>
       <c r="F12">
-        <v>12.91083952686304</v>
+        <v>5218.4548039</v>
       </c>
       <c r="G12">
-        <v>6.186333485876476</v>
+        <v>27334.14322387</v>
       </c>
       <c r="H12">
-        <v>9.369056444178138</v>
+        <v>7463.13156473</v>
       </c>
       <c r="I12">
-        <v>14.33547183529105</v>
+        <v>5720.6252526</v>
       </c>
       <c r="J12">
-        <v>21.15937677769958</v>
+        <v>2819.74298542</v>
       </c>
       <c r="K12">
-        <v>22.50918360903629</v>
+        <v>2786.28197115</v>
       </c>
       <c r="L12">
-        <v>3.524922954997809</v>
+        <v>81369.95049389001</v>
       </c>
       <c r="M12">
-        <v>4.547992356513719</v>
+        <v>40639.25023177</v>
       </c>
     </row>
     <row r="13">
@@ -6770,40 +10760,37 @@
         </is>
       </c>
       <c r="B13">
-        <v>6.406983106636615</v>
-      </c>
-      <c r="C13">
-        <v>96.02121278630497</v>
+        <v>32707.499524</v>
       </c>
       <c r="D13">
-        <v>10.20984819025989</v>
+        <v>11191.24476329</v>
       </c>
       <c r="E13">
-        <v>46.97601728566286</v>
+        <v>1040.21771394</v>
       </c>
       <c r="F13">
-        <v>12.21798004759873</v>
+        <v>7150.67094858</v>
       </c>
       <c r="G13">
-        <v>6.114261360457967</v>
+        <v>21759.78373378</v>
       </c>
       <c r="H13">
-        <v>8.273625427212753</v>
+        <v>11811.77089935</v>
       </c>
       <c r="I13">
-        <v>16.78805810303677</v>
+        <v>5448.66684699</v>
       </c>
       <c r="J13">
-        <v>18.89125792556847</v>
+        <v>3739.1547928</v>
       </c>
       <c r="K13">
-        <v>27.46612506041064</v>
+        <v>343.83544956</v>
       </c>
       <c r="L13">
-        <v>3.112184145273481</v>
+        <v>123861.14610292</v>
       </c>
       <c r="M13">
-        <v>4.75574555962989</v>
+        <v>30022.54432087</v>
       </c>
     </row>
     <row r="14">
@@ -6813,40 +10800,37 @@
         </is>
       </c>
       <c r="B14">
-        <v>5.694916652141218</v>
-      </c>
-      <c r="C14">
-        <v>54.25583893339033</v>
+        <v>35598.82668519</v>
       </c>
       <c r="D14">
-        <v>8.348433927152701</v>
+        <v>15764.49230674</v>
       </c>
       <c r="E14">
-        <v>34.55305181719793</v>
+        <v>1072.64153558</v>
       </c>
       <c r="F14">
-        <v>11.10854502738481</v>
+        <v>6720.92226263</v>
       </c>
       <c r="G14">
-        <v>5.222502559670898</v>
+        <v>36230.35545924</v>
       </c>
       <c r="H14">
-        <v>7.207470483101417</v>
+        <v>17356.76048435</v>
       </c>
       <c r="I14">
-        <v>15.31623358897622</v>
+        <v>6895.8168384</v>
       </c>
       <c r="J14">
-        <v>25.29672296696382</v>
+        <v>3458.58657059</v>
       </c>
       <c r="K14">
-        <v>18.11044522699582</v>
+        <v>2691.575031</v>
       </c>
       <c r="L14">
-        <v>2.920094090937093</v>
+        <v>127185.58821585</v>
       </c>
       <c r="M14">
-        <v>4.819951757678316</v>
+        <v>36174.99700035</v>
       </c>
     </row>
     <row r="15">
@@ -6856,40 +10840,34 @@
         </is>
       </c>
       <c r="B15">
-        <v>2.930426977011205</v>
-      </c>
-      <c r="C15">
-        <v>36.73463897757834</v>
+        <v>112176.03868358</v>
       </c>
       <c r="D15">
-        <v>5.749218696791174</v>
-      </c>
-      <c r="E15">
-        <v>33.4207311787026</v>
+        <v>27920.73408712</v>
       </c>
       <c r="F15">
-        <v>5.53671367929988</v>
+        <v>18513.20276421</v>
       </c>
       <c r="G15">
-        <v>3.327869045041671</v>
+        <v>74202.35635133</v>
       </c>
       <c r="H15">
-        <v>4.28373242361655</v>
+        <v>33499.51116839</v>
       </c>
       <c r="I15">
-        <v>8.027844021476463</v>
+        <v>16680.98747064</v>
       </c>
       <c r="J15">
-        <v>11.70386834744208</v>
+        <v>2892.73850481</v>
       </c>
       <c r="K15">
-        <v>9.938929847658766</v>
+        <v>12364.15048422</v>
       </c>
       <c r="L15">
-        <v>1.557757617411191</v>
+        <v>371535.93561262</v>
       </c>
       <c r="M15">
-        <v>2.49826722025525</v>
+        <v>124056.13380581</v>
       </c>
     </row>
   </sheetData>
@@ -6976,40 +10954,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>4.492092511807615</v>
+        <v>666572.2465374001</v>
       </c>
       <c r="C2">
-        <v>40.01368302042479</v>
+        <v>10721.39398632</v>
       </c>
       <c r="D2">
-        <v>8.571701561965645</v>
+        <v>225132.43250087</v>
       </c>
       <c r="E2">
-        <v>28.51031301533897</v>
+        <v>13930.08508954</v>
       </c>
       <c r="F2">
-        <v>8.93639338846166</v>
+        <v>131839.36280077</v>
       </c>
       <c r="G2">
-        <v>5.229669377832169</v>
+        <v>289756.29552556</v>
       </c>
       <c r="H2">
-        <v>10.39798790709522</v>
+        <v>134630.13526001</v>
       </c>
       <c r="I2">
-        <v>15.49339093352479</v>
+        <v>60607.36486665</v>
       </c>
       <c r="J2">
-        <v>23.40295900396184</v>
+        <v>25533.47632362</v>
       </c>
       <c r="K2">
-        <v>23.43866016278162</v>
+        <v>25578.8187439</v>
       </c>
       <c r="L2">
-        <v>3.717158915935268</v>
+        <v>1388023.09968044</v>
       </c>
       <c r="M2">
-        <v>4.251886293753512</v>
+        <v>864724.85622401</v>
       </c>
     </row>
     <row r="3">
@@ -7019,40 +10997,37 @@
         </is>
       </c>
       <c r="B3">
-        <v>4.918897857141927</v>
+        <v>850148.8477376</v>
       </c>
       <c r="C3">
-        <v>53.58375536282697</v>
+        <v>10082.10465552</v>
       </c>
       <c r="D3">
-        <v>8.743835684360867</v>
-      </c>
-      <c r="E3">
-        <v>32.92932076322173</v>
+        <v>224333.837643</v>
       </c>
       <c r="F3">
-        <v>10.66659869662422</v>
+        <v>170866.00922546</v>
       </c>
       <c r="G3">
-        <v>5.36125177901086</v>
+        <v>338699.30829528</v>
       </c>
       <c r="H3">
-        <v>9.989623998042067</v>
+        <v>118915.5670959</v>
       </c>
       <c r="I3">
-        <v>17.25381716472012</v>
+        <v>75158.03351896</v>
       </c>
       <c r="J3">
-        <v>24.69964002518831</v>
+        <v>34504.85934592</v>
       </c>
       <c r="K3">
-        <v>25.92994165808681</v>
+        <v>47587.546159</v>
       </c>
       <c r="L3">
-        <v>3.668225128744571</v>
+        <v>1742558.49527814</v>
       </c>
       <c r="M3">
-        <v>3.838607004139023</v>
+        <v>899751.41083021</v>
       </c>
     </row>
     <row r="4">
@@ -7062,40 +11037,37 @@
         </is>
       </c>
       <c r="B4">
-        <v>5.058131110250899</v>
+        <v>666457.5710363</v>
       </c>
       <c r="C4">
-        <v>61.63728985672238</v>
+        <v>2780.50693607</v>
       </c>
       <c r="D4">
-        <v>8.946831562393742</v>
-      </c>
-      <c r="E4">
-        <v>44.04029700196073</v>
+        <v>217243.61110671</v>
       </c>
       <c r="F4">
-        <v>9.796483975264744</v>
+        <v>230836.28595987</v>
       </c>
       <c r="G4">
-        <v>5.550895340721362</v>
+        <v>465752.58749005</v>
       </c>
       <c r="H4">
-        <v>11.91842730387769</v>
+        <v>143354.61619409</v>
       </c>
       <c r="I4">
-        <v>39.59298644211017</v>
+        <v>47289.08975739</v>
       </c>
       <c r="J4">
-        <v>34.09287620106893</v>
+        <v>9955.200820779999</v>
       </c>
       <c r="K4">
-        <v>30.23289690893845</v>
+        <v>55523.1044049</v>
       </c>
       <c r="L4">
-        <v>3.605533697143904</v>
+        <v>1712612.11264376</v>
       </c>
       <c r="M4">
-        <v>3.406317436025092</v>
+        <v>1010415.36730785</v>
       </c>
     </row>
     <row r="5">
@@ -7105,40 +11077,34 @@
         </is>
       </c>
       <c r="B5">
-        <v>5.029101910509449</v>
-      </c>
-      <c r="C5">
-        <v>53.51312726801902</v>
+        <v>782533.65017358</v>
       </c>
       <c r="D5">
-        <v>12.35723942527865</v>
-      </c>
-      <c r="E5">
-        <v>33.06175095164849</v>
+        <v>221893.50192605</v>
       </c>
       <c r="F5">
-        <v>10.99593432222137</v>
+        <v>147011.89771075</v>
       </c>
       <c r="G5">
-        <v>5.487754874826761</v>
+        <v>485297.47871318</v>
       </c>
       <c r="H5">
-        <v>12.06265515743659</v>
+        <v>125655.65116034</v>
       </c>
       <c r="I5">
-        <v>22.80938686817856</v>
+        <v>13833.60064455</v>
       </c>
       <c r="J5">
-        <v>39.95237793973855</v>
+        <v>13161.09105555</v>
       </c>
       <c r="K5">
-        <v>27.61371061891656</v>
+        <v>6085.411116019999</v>
       </c>
       <c r="L5">
-        <v>3.600849356364903</v>
+        <v>1517241.87530838</v>
       </c>
       <c r="M5">
-        <v>3.866715216734959</v>
+        <v>1056577.92738027</v>
       </c>
     </row>
     <row r="6">
@@ -7148,40 +11114,37 @@
         </is>
       </c>
       <c r="B6">
-        <v>5.689866289303238</v>
-      </c>
-      <c r="C6">
-        <v>94.83573914981882</v>
+        <v>702344.50298054</v>
       </c>
       <c r="D6">
-        <v>9.538665101764051</v>
+        <v>183667.05339051</v>
       </c>
       <c r="E6">
-        <v>49.35135457361289</v>
+        <v>6359.79873984</v>
       </c>
       <c r="F6">
-        <v>12.13623130328289</v>
+        <v>47472.6188405</v>
       </c>
       <c r="G6">
-        <v>5.674670719377591</v>
+        <v>265738.24566367</v>
       </c>
       <c r="H6">
-        <v>10.39152103765723</v>
+        <v>147113.36351632</v>
       </c>
       <c r="I6">
-        <v>24.94061927781581</v>
+        <v>23163.20724464</v>
       </c>
       <c r="J6">
-        <v>33.13157709683888</v>
+        <v>4223.3827618</v>
       </c>
       <c r="K6">
-        <v>30.58623707642459</v>
+        <v>8996.764264450001</v>
       </c>
       <c r="L6">
-        <v>4.018091704529857</v>
+        <v>1295824.64563804</v>
       </c>
       <c r="M6">
-        <v>4.991481916555285</v>
+        <v>801415.04470877</v>
       </c>
     </row>
     <row r="7">
@@ -7191,40 +11154,34 @@
         </is>
       </c>
       <c r="B7">
-        <v>5.606014375764952</v>
-      </c>
-      <c r="C7">
-        <v>104.2846320532687</v>
+        <v>1070698.87353972</v>
       </c>
       <c r="D7">
-        <v>8.931298984101463</v>
-      </c>
-      <c r="E7">
-        <v>39.75541492523889</v>
+        <v>112030.32449808</v>
       </c>
       <c r="F7">
-        <v>12.31004972244459</v>
+        <v>146094.94174061</v>
       </c>
       <c r="G7">
-        <v>5.623178822784276</v>
+        <v>365041.35281516</v>
       </c>
       <c r="H7">
-        <v>10.67777664448757</v>
+        <v>236541.05297348</v>
       </c>
       <c r="I7">
-        <v>16.83310695950629</v>
+        <v>41494.25900098</v>
       </c>
       <c r="J7">
-        <v>22.96476931606498</v>
+        <v>6621.19771546</v>
       </c>
       <c r="K7">
-        <v>21.77051780738274</v>
+        <v>35717.85502889</v>
       </c>
       <c r="L7">
-        <v>3.792273454461526</v>
+        <v>1686246.18316794</v>
       </c>
       <c r="M7">
-        <v>4.319865368975295</v>
+        <v>740505.41473417</v>
       </c>
     </row>
     <row r="8">
@@ -7234,40 +11191,37 @@
         </is>
       </c>
       <c r="B8">
-        <v>4.984491711099794</v>
-      </c>
-      <c r="C8">
-        <v>49.42701172036979</v>
+        <v>886566.4765217</v>
       </c>
       <c r="D8">
-        <v>8.332624798393086</v>
+        <v>213263.56832598</v>
       </c>
       <c r="E8">
-        <v>39.64207136705289</v>
+        <v>6979.60466304</v>
       </c>
       <c r="F8">
-        <v>10.6296470976006</v>
+        <v>187952.90506413</v>
       </c>
       <c r="G8">
-        <v>5.651213027708482</v>
+        <v>561178.13852454</v>
       </c>
       <c r="H8">
-        <v>9.676950758984544</v>
+        <v>170104.4826053</v>
       </c>
       <c r="I8">
-        <v>19.05135937652802</v>
+        <v>30452.24189459</v>
       </c>
       <c r="J8">
-        <v>39.38440314232446</v>
+        <v>4881.9654019</v>
       </c>
       <c r="K8">
-        <v>31.17333294499889</v>
+        <v>18383.9978713</v>
       </c>
       <c r="L8">
-        <v>3.329759763362078</v>
+        <v>1579318.35102105</v>
       </c>
       <c r="M8">
-        <v>4.662151006897863</v>
+        <v>741771.6655864801</v>
       </c>
     </row>
     <row r="9">
@@ -7277,40 +11231,37 @@
         </is>
       </c>
       <c r="B9">
-        <v>5.287481770470878</v>
+        <v>906117.429735</v>
       </c>
       <c r="C9">
-        <v>55.5214316775406</v>
+        <v>1709.0309305</v>
       </c>
       <c r="D9">
-        <v>12.77405578484473</v>
-      </c>
-      <c r="E9">
-        <v>71.74606365002585</v>
+        <v>184589.41017338</v>
       </c>
       <c r="F9">
-        <v>12.92943327655416</v>
+        <v>93760.66951820999</v>
       </c>
       <c r="G9">
-        <v>5.675263086855168</v>
+        <v>408868.00033361</v>
       </c>
       <c r="H9">
-        <v>10.6685650220267</v>
+        <v>126008.7752829</v>
       </c>
       <c r="I9">
-        <v>19.490025762307</v>
+        <v>40033.3017117</v>
       </c>
       <c r="J9">
-        <v>26.55998449633026</v>
+        <v>31296.12663786</v>
       </c>
       <c r="K9">
-        <v>32.23723772008246</v>
+        <v>25166.0217987</v>
       </c>
       <c r="L9">
-        <v>3.159801571049323</v>
+        <v>1701863.77381794</v>
       </c>
       <c r="M9">
-        <v>4.115020371920123</v>
+        <v>727643.190065</v>
       </c>
     </row>
     <row r="10">
@@ -7320,40 +11271,34 @@
         </is>
       </c>
       <c r="B10">
-        <v>7.217968530013056</v>
-      </c>
-      <c r="C10">
-        <v>70.06628679983895</v>
+        <v>780210.78958353</v>
       </c>
       <c r="D10">
-        <v>11.31336915874272</v>
-      </c>
-      <c r="E10">
-        <v>85.09057203798621</v>
+        <v>80977.97326023001</v>
       </c>
       <c r="F10">
-        <v>25.85967562673568</v>
+        <v>53460.78271535</v>
       </c>
       <c r="G10">
-        <v>8.981035491238798</v>
+        <v>180282.67792225</v>
       </c>
       <c r="H10">
-        <v>14.92886764458343</v>
+        <v>30356.35034206</v>
       </c>
       <c r="I10">
-        <v>21.61204690957359</v>
+        <v>57808.96041389</v>
       </c>
       <c r="J10">
-        <v>30.05389862011868</v>
+        <v>5971.0621158</v>
       </c>
       <c r="K10">
-        <v>26.97650835014687</v>
+        <v>15014.322301</v>
       </c>
       <c r="L10">
-        <v>5.062531052690753</v>
+        <v>1231026.30249328</v>
       </c>
       <c r="M10">
-        <v>4.955301404208411</v>
+        <v>661097.6594761</v>
       </c>
     </row>
     <row r="11">
@@ -7363,40 +11308,37 @@
         </is>
       </c>
       <c r="B11">
-        <v>8.056961567714012</v>
+        <v>425122.76651073</v>
       </c>
       <c r="C11">
-        <v>52.03466914524306</v>
+        <v>9153.413098200001</v>
       </c>
       <c r="D11">
-        <v>12.69682213825984</v>
-      </c>
-      <c r="E11">
-        <v>65.45108040607579</v>
+        <v>101941.78063607</v>
       </c>
       <c r="F11">
-        <v>13.03351622692987</v>
+        <v>96496.59536002</v>
       </c>
       <c r="G11">
-        <v>9.521459776881812</v>
+        <v>424813.69084408</v>
       </c>
       <c r="H11">
-        <v>13.40588659645215</v>
+        <v>65375.85774521</v>
       </c>
       <c r="I11">
-        <v>24.9238940162734</v>
+        <v>72477.73591592</v>
       </c>
       <c r="J11">
-        <v>33.73295847501409</v>
+        <v>6711.7199208</v>
       </c>
       <c r="K11">
-        <v>34.08872863649473</v>
+        <v>9144.233225260001</v>
       </c>
       <c r="L11">
-        <v>5.203997835165775</v>
+        <v>992661.74428112</v>
       </c>
       <c r="M11">
-        <v>5.284569893589095</v>
+        <v>629499.39529298</v>
       </c>
     </row>
     <row r="12">
@@ -7406,40 +11348,37 @@
         </is>
       </c>
       <c r="B12">
-        <v>7.565085250097002</v>
+        <v>618125.8354027</v>
       </c>
       <c r="C12">
-        <v>56.3250116660894</v>
+        <v>4717.95226911</v>
       </c>
       <c r="D12">
-        <v>14.42768447433914</v>
-      </c>
-      <c r="E12">
-        <v>53.61960437147341</v>
+        <v>144855.90352286</v>
       </c>
       <c r="F12">
-        <v>13.53251623657362</v>
+        <v>62961.7413653</v>
       </c>
       <c r="G12">
-        <v>7.060847350341315</v>
+        <v>387335.19971241</v>
       </c>
       <c r="H12">
-        <v>10.55927827258207</v>
+        <v>130606.54024695</v>
       </c>
       <c r="I12">
-        <v>16.64578996901918</v>
+        <v>99958.12481661</v>
       </c>
       <c r="J12">
-        <v>24.07805410409969</v>
+        <v>22927.27952782</v>
       </c>
       <c r="K12">
-        <v>25.28305041811591</v>
+        <v>50575.2773875</v>
       </c>
       <c r="L12">
-        <v>4.143553779921012</v>
+        <v>1195883.93041618</v>
       </c>
       <c r="M12">
-        <v>5.081344572914241</v>
+        <v>722607.99605344</v>
       </c>
     </row>
     <row r="13">
@@ -7449,40 +11388,37 @@
         </is>
       </c>
       <c r="B13">
-        <v>6.522211796233711</v>
-      </c>
-      <c r="C13">
-        <v>100.3198716657155</v>
+        <v>560925.10991627</v>
       </c>
       <c r="D13">
-        <v>15.50593083312338</v>
+        <v>169804.21051088</v>
       </c>
       <c r="E13">
-        <v>57.12602584664103</v>
+        <v>15144.07806192</v>
       </c>
       <c r="F13">
-        <v>14.35979951340064</v>
+        <v>101874.42903878</v>
       </c>
       <c r="G13">
-        <v>7.022905514510799</v>
+        <v>354680.62328842</v>
       </c>
       <c r="H13">
-        <v>8.644560839633092</v>
+        <v>216348.45319323</v>
       </c>
       <c r="I13">
-        <v>17.83802058438342</v>
+        <v>124596.78967325</v>
       </c>
       <c r="J13">
-        <v>22.54474920056573</v>
+        <v>67908.35641492999</v>
       </c>
       <c r="K13">
-        <v>29.38765668599693</v>
+        <v>5157.5317434</v>
       </c>
       <c r="L13">
-        <v>3.907877720859591</v>
+        <v>1859073.62167098</v>
       </c>
       <c r="M13">
-        <v>4.901635130115908</v>
+        <v>625436.7292404399</v>
       </c>
     </row>
     <row r="14">
@@ -7492,40 +11428,37 @@
         </is>
       </c>
       <c r="B14">
-        <v>6.345468937315263</v>
-      </c>
-      <c r="C14">
-        <v>52.91306685205372</v>
+        <v>595491.86357025</v>
       </c>
       <c r="D14">
-        <v>9.961322375320306</v>
+        <v>239307.59681731</v>
       </c>
       <c r="E14">
-        <v>40.00466526822849</v>
+        <v>21452.8307116</v>
       </c>
       <c r="F14">
-        <v>12.60952182286766</v>
+        <v>128503.34751557</v>
       </c>
       <c r="G14">
-        <v>6.072151758758413</v>
+        <v>576983.00260953</v>
       </c>
       <c r="H14">
-        <v>8.319811323789924</v>
+        <v>257343.77668794</v>
       </c>
       <c r="I14">
-        <v>16.42621395810422</v>
+        <v>138080.62127203</v>
       </c>
       <c r="J14">
-        <v>27.73810831133213</v>
+        <v>75246.25260681</v>
       </c>
       <c r="K14">
-        <v>25.93222085458164</v>
+        <v>43391.5429104</v>
       </c>
       <c r="L14">
-        <v>3.093098338976354</v>
+        <v>1982801.70487574</v>
       </c>
       <c r="M14">
-        <v>5.043890718477585</v>
+        <v>820937.50982482</v>
       </c>
     </row>
     <row r="15">
@@ -7535,40 +11468,34 @@
         </is>
       </c>
       <c r="B15">
-        <v>3.402830659205338</v>
-      </c>
-      <c r="C15">
-        <v>36.34445454249064</v>
+        <v>1830829.94359026</v>
       </c>
       <c r="D15">
-        <v>8.950636552235839</v>
-      </c>
-      <c r="E15">
-        <v>33.38993001966375</v>
+        <v>492220.08924118</v>
       </c>
       <c r="F15">
-        <v>6.162371086775511</v>
+        <v>322398.39274928</v>
       </c>
       <c r="G15">
-        <v>3.715142888987211</v>
+        <v>1290035.31888421</v>
       </c>
       <c r="H15">
-        <v>5.498355381102868</v>
+        <v>585968.10883834</v>
       </c>
       <c r="I15">
-        <v>8.990989284410613</v>
+        <v>277342.86872456</v>
       </c>
       <c r="J15">
-        <v>14.69840145252728</v>
+        <v>36522.58701203</v>
       </c>
       <c r="K15">
-        <v>12.10787057418992</v>
+        <v>156770.16987371</v>
       </c>
       <c r="L15">
-        <v>1.747755610813695</v>
+        <v>5881671.69644798</v>
       </c>
       <c r="M15">
-        <v>2.771068401953933</v>
+        <v>2400084.96342771</v>
       </c>
     </row>
   </sheetData>
